--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C922A3C7-15B9-48B1-84E1-20D5B704898B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D230B5D-BA5A-43ED-AE0A-64C916B072D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t>Date</t>
   </si>
@@ -355,6 +357,15 @@
   </si>
   <si>
     <t>Final Midterm report completion and submission</t>
+  </si>
+  <si>
+    <t>generated dispatch module front end (updated FarmerDashboard.jsx,dashboard.css)</t>
+  </si>
+  <si>
+    <t>generated dispatch module backend (DispatchController.cs,CreateDispatchDTO.cs,)</t>
+  </si>
+  <si>
+    <t>sorted issue on create dispatch with select request</t>
   </si>
 </sst>
 </file>
@@ -614,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -669,27 +680,84 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -701,66 +769,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,362 +1049,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="164.25" customHeight="1">
-      <c r="A2" s="26">
-        <v>46035</v>
-      </c>
-      <c r="B2" s="28">
-        <v>2</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="31"/>
-    </row>
-    <row r="4" spans="1:3" ht="165.75" thickBot="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="180.75" thickBot="1">
-      <c r="A5" s="10">
-        <v>46036</v>
-      </c>
-      <c r="B5" s="8">
-        <v>4</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A6" s="3">
-        <v>46037</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="4">
-        <v>4</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="60.75" thickBot="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="60.75" thickBot="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="45">
-      <c r="A10" s="12"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="9"/>
-    </row>
-    <row r="12" spans="1:3" ht="150" customHeight="1">
-      <c r="A12" s="26">
-        <v>46039</v>
-      </c>
-      <c r="B12" s="28">
-        <v>2</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="32"/>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" spans="1:3" ht="150.75" thickBot="1">
-      <c r="A15" s="10">
-        <v>46042</v>
-      </c>
-      <c r="B15" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="135.75" thickBot="1">
-      <c r="A16" s="10">
-        <v>46043</v>
-      </c>
-      <c r="B16" s="8">
-        <v>2</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="90.75" thickBot="1">
-      <c r="A17" s="10">
-        <v>46044</v>
-      </c>
-      <c r="B17" s="8">
-        <v>2</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="90.75" thickBot="1">
-      <c r="A18" s="3">
-        <v>46046</v>
-      </c>
-      <c r="B18" s="8">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8">
-        <v>2</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A20" s="10">
-        <v>46047</v>
-      </c>
-      <c r="B20" s="8">
-        <v>2</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A21" s="10">
-        <v>46048</v>
-      </c>
-      <c r="B21" s="8">
-        <v>1</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="120">
-      <c r="A22" s="26">
-        <v>46049</v>
-      </c>
-      <c r="B22" s="28">
-        <v>3</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A23" s="27"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="105">
-      <c r="A24" s="26">
-        <v>46051</v>
-      </c>
-      <c r="B24" s="28">
-        <v>4</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="90.75" thickBot="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="120.75" thickBot="1">
-      <c r="A26" s="10">
-        <v>46055</v>
-      </c>
-      <c r="B26" s="8">
-        <v>2</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="150">
-      <c r="A27" s="26">
-        <v>46057</v>
-      </c>
-      <c r="B27" s="28">
-        <v>3</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="90.75" thickBot="1">
-      <c r="A29" s="10">
-        <v>46058</v>
-      </c>
-      <c r="B29" s="8">
-        <v>2</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="210.75" thickBot="1">
-      <c r="A30" s="10">
-        <v>46061</v>
-      </c>
-      <c r="B30" s="8">
-        <v>3</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="105.75" thickBot="1">
-      <c r="A31" s="3">
-        <v>46062</v>
-      </c>
-      <c r="B31" s="4">
-        <v>5</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="75">
-      <c r="A32" s="22"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="75">
-      <c r="A33" s="22"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="75">
-      <c r="A34" s="22"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="75.75" thickBot="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C48B184-BD77-49CB-976B-CD2845F9E4FF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE14CD6-E8F7-4785-AF16-07A58E8D9E8B}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1416,20 +1070,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="26">
+      <c r="A2" s="44">
         <v>46035</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="46">
         <v>2</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="50"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1496,20 +1150,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="26">
+      <c r="A12" s="44">
         <v>46039</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="46">
         <v>2</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="49" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="32"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="51"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1592,10 +1246,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="26">
+      <c r="A22" s="44">
         <v>46049</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="46">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1603,17 +1257,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="27"/>
-      <c r="B23" s="25"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="26">
+      <c r="A24" s="44">
         <v>46051</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="46">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1621,8 +1275,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="25"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="47"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1639,10 +1293,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="26">
+      <c r="A27" s="44">
         <v>46057</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="46">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1650,8 +1304,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="25"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="47"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -1690,29 +1344,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="24"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="22"/>
-      <c r="B33" s="24"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="22"/>
-      <c r="B34" s="24"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="22"/>
-      <c r="B35" s="24"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -1838,8 +1492,35 @@
       </c>
     </row>
     <row r="55" spans="1:3">
+      <c r="A55" s="17">
+        <v>46077</v>
+      </c>
       <c r="C55" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="17">
+        <v>46081</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="17">
+        <v>46082</v>
+      </c>
+      <c r="C57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="17">
+        <v>46083</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1864,449 +1545,449 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
   <dimension ref="B2:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" style="33" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="33" customWidth="1"/>
-    <col min="4" max="4" width="82.28515625" style="33" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="22" customWidth="1"/>
+    <col min="4" max="4" width="82.28515625" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="26" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="30">
-      <c r="B3" s="47">
+      <c r="B3" s="36">
         <v>46035</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="29">
         <v>2</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="42"/>
-      <c r="C4" s="40">
+      <c r="B4" s="31"/>
+      <c r="C4" s="29">
         <v>1</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="28" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="30">
-      <c r="B5" s="51">
+      <c r="B5" s="40">
         <v>46036</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="30">
         <v>4</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="28" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="47">
+      <c r="B6" s="36">
         <v>46037</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="30">
         <v>4</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="40" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="29" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="40" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="29" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="40" t="s">
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="29" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="40" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="29" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="46">
+      <c r="B11" s="35">
         <v>46039</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="31">
         <v>2</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="28" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="38">
+      <c r="B12" s="27">
         <v>46042</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="28">
         <v>0.5</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="28" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="38">
+      <c r="B13" s="27">
         <v>46043</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="28">
         <v>2</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="28" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="47">
+      <c r="B14" s="36">
         <v>46044</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="28">
         <v>2</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="28" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="47">
+      <c r="B15" s="36">
         <v>46046</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="29">
         <v>2</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="28" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="42"/>
-      <c r="C16" s="40">
+      <c r="B16" s="31"/>
+      <c r="C16" s="29">
         <v>2</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="46">
+      <c r="B17" s="35">
         <v>46047</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="28">
         <v>2</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="38">
+      <c r="B18" s="27">
         <v>46048</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="28">
         <v>1</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="28" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="47">
+      <c r="B19" s="36">
         <v>46049</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="28">
         <v>3</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="47">
+      <c r="B20" s="36">
         <v>46051</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="29">
         <v>4</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="28" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="42"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="39" t="s">
+      <c r="B21" s="31"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="28" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="51">
+      <c r="B22" s="40">
         <v>46055</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="30">
         <v>2</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="28" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="47">
+      <c r="B23" s="36">
         <v>46057</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="30">
         <v>3</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="29" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="40" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="29" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="38">
+      <c r="B25" s="27">
         <v>46058</v>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="28">
         <v>2</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="29" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="47">
+      <c r="B26" s="36">
         <v>46061</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="30">
         <v>4</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="29" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="40" t="s">
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="29" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="47">
+      <c r="B28" s="36">
         <v>46062</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="30">
         <v>5</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="29" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="40" t="s">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="29" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="40" t="s">
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="29" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="40" t="s">
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="47">
+      <c r="B32" s="36">
         <v>46063</v>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="30">
         <v>5</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="29" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="40" t="s">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="29" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="47">
+      <c r="B34" s="36">
         <v>46065</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="30">
         <v>4</v>
       </c>
-      <c r="D34" s="40" t="s">
+      <c r="D34" s="29" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="40" t="s">
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="47">
+      <c r="B36" s="36">
         <v>46068</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="30">
         <v>5</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="29" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="42"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="40" t="s">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="29" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="51">
+      <c r="B38" s="40">
         <v>46070</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="23">
         <v>6</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D38" s="29" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="30">
-      <c r="B39" s="43"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="40" t="s">
+      <c r="B39" s="32"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="29" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="43"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="40" t="s">
+      <c r="B40" s="32"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="29" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="43"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="40" t="s">
+      <c r="B41" s="32"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="29" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="43"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="40" t="s">
+      <c r="B42" s="32"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="29" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="43"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="40" t="s">
+      <c r="B43" s="32"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="29" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="2:4">
-      <c r="B44" s="42"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="40" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="29" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="30">
-      <c r="B45" s="51">
+      <c r="B45" s="40">
         <v>46071</v>
       </c>
-      <c r="C45" s="43">
+      <c r="C45" s="32">
         <v>6</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="28" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="46" spans="2:4">
-      <c r="B46" s="47">
+      <c r="B46" s="36">
         <v>46076</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="33">
         <v>8</v>
       </c>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="29" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="30">
-      <c r="B47" s="43"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="40" t="s">
+      <c r="B47" s="32"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="29" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:4">
-      <c r="B48" s="49"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="48" t="s">
+      <c r="B48" s="38"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="37" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="49" spans="2:4">
-      <c r="B49" s="50"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="48" t="s">
+      <c r="B49" s="39"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="37" t="s">
         <v>95</v>
       </c>
     </row>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D230B5D-BA5A-43ED-AE0A-64C916B072D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EAF831-5520-46AE-9AAA-29B37518ABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -365,7 +365,10 @@
     <t>generated dispatch module backend (DispatchController.cs,CreateDispatchDTO.cs,)</t>
   </si>
   <si>
-    <t>sorted issue on create dispatch with select request</t>
+    <t>sorted issue on create dispatch with select request: solution:dispatchid initialized in back end is different with frontend</t>
+  </si>
+  <si>
+    <t>sorted issue on updating dispatched items on model submission:solution:demandRequestId id not defined in backend controller farmercontroller.cs</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE14CD6-E8F7-4785-AF16-07A58E8D9E8B}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1521,6 +1524,11 @@
       </c>
       <c r="C58" s="21" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="C59" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EAF831-5520-46AE-9AAA-29B37518ABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BD83EC-5C7C-4B8A-A2D4-F22C214F8E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>sorted issue on updating dispatched items on model submission:solution:demandRequestId id not defined in backend controller farmercontroller.cs</t>
+  </si>
+  <si>
+    <t>created outlet element for nested pages in requireAuth and RequireRole.jsx</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE14CD6-E8F7-4785-AF16-07A58E8D9E8B}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1529,6 +1532,11 @@
     <row r="59" spans="1:3">
       <c r="C59" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="C60" s="21" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BD83EC-5C7C-4B8A-A2D4-F22C214F8E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3E87DE-81F3-4300-B656-A37D277447F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -372,6 +372,12 @@
   </si>
   <si>
     <t>created outlet element for nested pages in requireAuth and RequireRole.jsx</t>
+  </si>
+  <si>
+    <t>completed farmer product frontend and backend (FarmerProducts.jsx,farmerController.csProductsController.cs,InventoryLotDTO.CS,UpdateInventoryLotDTO.cs)</t>
+  </si>
+  <si>
+    <t>completed farmer request window both frontend and backend functionality(FarmerController.cs,FarmerDemandRequestRowDto.cs,FarmerRequests.jsx)</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE14CD6-E8F7-4785-AF16-07A58E8D9E8B}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1537,6 +1543,16 @@
     <row r="60" spans="1:3">
       <c r="C60" s="21" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="C61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="C62" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1563,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:D49"/>
+  <dimension ref="B2:D57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="22" customWidth="1"/>
@@ -2007,6 +2023,70 @@
         <v>95</v>
       </c>
     </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="17">
+        <v>46077</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="17">
+        <v>46081</v>
+      </c>
+      <c r="C51"/>
+      <c r="D51" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="17">
+        <v>46082</v>
+      </c>
+      <c r="C52"/>
+      <c r="D52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="17">
+        <v>46083</v>
+      </c>
+      <c r="C53"/>
+      <c r="D53" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3E87DE-81F3-4300-B656-A37D277447F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2649E632-7467-4A0F-8506-3BF75440515A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>completed farmer request window both frontend and backend functionality(FarmerController.cs,FarmerDemandRequestRowDto.cs,FarmerRequests.jsx)</t>
+  </si>
+  <si>
+    <t>DispatchRowDto.cs,UpdateDispatchStatusDto.cs</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:D57"/>
+  <dimension ref="B2:D58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="22" customWidth="1"/>
@@ -2087,6 +2090,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="58" spans="2:4">
+      <c r="D58" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2649E632-7467-4A0F-8506-3BF75440515A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B62938-5AC7-4AA4-830E-1B3A3BC000D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,7 +380,7 @@
     <t>completed farmer request window both frontend and backend functionality(FarmerController.cs,FarmerDemandRequestRowDto.cs,FarmerRequests.jsx)</t>
   </si>
   <si>
-    <t>DispatchRowDto.cs,UpdateDispatchStatusDto.cs</t>
+    <t>completed farmer dispatch window(DispatchRowDto.cs,UpdateDispatchStatusDto.cs,FarmerDispatchController.cs,FarmerDispatch.jsx)</t>
   </si>
 </sst>
 </file>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B62938-5AC7-4AA4-830E-1B3A3BC000D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21FEA08-CB76-4569-BE28-D77B4C429A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -380,7 +380,31 @@
     <t>completed farmer request window both frontend and backend functionality(FarmerController.cs,FarmerDemandRequestRowDto.cs,FarmerRequests.jsx)</t>
   </si>
   <si>
-    <t>completed farmer dispatch window(DispatchRowDto.cs,UpdateDispatchStatusDto.cs,FarmerDispatchController.cs,FarmerDispatch.jsx)</t>
+    <t>Implemented API endpoint POST /api/farmer/inventorylots using CreateInventoryLotDto and InventoryLotsController</t>
+  </si>
+  <si>
+    <t>Developed Dispatch module (frontend) and updated UI styles (FarmerDashboard.jsx, dashboard.css)</t>
+  </si>
+  <si>
+    <t>Implemented Dispatch module (backend) (DispatchController.cs, CreateDispatchDto.cs)</t>
+  </si>
+  <si>
+    <t>Fixed Create Dispatch - select request issue by aligning backend dispatch initialization and frontend handling</t>
+  </si>
+  <si>
+    <t>Fixed Dispatched items update issue by adding/returning demandRequestId correctly in FarmerController.cs</t>
+  </si>
+  <si>
+    <t>Implemented nested routing support by adding Outlet in RequireAuth and RequireRole.jsx</t>
+  </si>
+  <si>
+    <t>Completed Farmer Products page frontend + backend (FarmerProducts.jsx, FarmerController.cs / ProductsController.cs, InventoryLotDto.cs, UpdateInventoryLotDto.cs)</t>
+  </si>
+  <si>
+    <t>Completed Farmer Requests page frontend + backend (FarmerController.cs, FarmerDemandRequestRowDto.cs, FarmerRequests.jsx)</t>
+  </si>
+  <si>
+    <t>Completed Farmer Dispatch page frontend + backend (DispatchRowDto.cs, UpdateDispatchStatusDto.cs, FarmerDispatchController.cs, FarmerDispatch.jsx)</t>
   </si>
 </sst>
 </file>
@@ -640,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -783,6 +807,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2026,76 +2071,79 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="17">
+    <row r="50" spans="2:4" ht="30">
+      <c r="B50" s="52">
         <v>46077</v>
       </c>
-      <c r="C50"/>
-      <c r="D50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="17">
+      <c r="C50" s="53"/>
+      <c r="D50" s="54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="30">
+      <c r="B51" s="52">
         <v>46081</v>
       </c>
-      <c r="C51"/>
-      <c r="D51" s="21" t="s">
-        <v>96</v>
+      <c r="C51" s="53"/>
+      <c r="D51" s="54" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="2:4">
-      <c r="B52" s="17">
+      <c r="B52" s="52">
         <v>46082</v>
       </c>
-      <c r="C52"/>
-      <c r="D52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="17">
+      <c r="C52" s="53"/>
+      <c r="D52" s="54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="30">
+      <c r="B53" s="55">
         <v>46083</v>
       </c>
-      <c r="C53"/>
-      <c r="D53" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55" s="21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57" s="21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="D58" t="s">
-        <v>103</v>
+      <c r="C53" s="58"/>
+      <c r="D53" s="54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="30">
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="30">
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="54" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="45">
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="30">
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="30">
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="54" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,19 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\working\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21FEA08-CB76-4569-BE28-D77B4C429A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD354402-BD7B-4756-AB91-3FA51FF2EDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -405,6 +404,15 @@
   </si>
   <si>
     <t>Completed Farmer Dispatch page frontend + backend (DispatchRowDto.cs, UpdateDispatchStatusDto.cs, FarmerDispatchController.cs, FarmerDispatch.jsx)</t>
+  </si>
+  <si>
+    <t>submitted</t>
+  </si>
+  <si>
+    <t>update vendor dashboard(create dispatch model including filesvendorDashboard.jsx,VendorDemandRequestsController.cs)</t>
+  </si>
+  <si>
+    <t>fully integrated create demand request modal</t>
   </si>
 </sst>
 </file>
@@ -451,18 +459,12 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -717,8 +719,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -731,7 +731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -776,60 +776,62 @@
     <xf numFmtId="16" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1110,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE14CD6-E8F7-4785-AF16-07A58E8D9E8B}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1130,20 +1132,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="44">
+      <c r="A2" s="47">
         <v>46035</v>
       </c>
-      <c r="B2" s="46">
+      <c r="B2" s="49">
         <v>2</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
       <c r="A3" s="48"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="52"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1210,20 +1212,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="44">
+      <c r="A12" s="47">
         <v>46039</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="49">
         <v>2</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="51" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="48"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="51"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1306,10 +1308,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="44">
+      <c r="A22" s="47">
         <v>46049</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="49">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1317,17 +1319,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="56"/>
+      <c r="B23" s="50"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="44">
+      <c r="A24" s="47">
         <v>46051</v>
       </c>
-      <c r="B24" s="46">
+      <c r="B24" s="49">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1335,8 +1337,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="47"/>
+      <c r="A25" s="56"/>
+      <c r="B25" s="50"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1353,10 +1355,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="44">
+      <c r="A27" s="47">
         <v>46057</v>
       </c>
-      <c r="B27" s="46">
+      <c r="B27" s="49">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1364,8 +1366,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="45"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="50"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -1404,29 +1406,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="53"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="42"/>
-      <c r="B33" s="43"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="42"/>
-      <c r="B34" s="43"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="53"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -1515,102 +1517,115 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:4">
       <c r="A49" s="17">
         <v>46071</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="57" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="C50" s="21" t="s">
+    <row r="50" spans="1:4">
+      <c r="C50" s="58" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="C51" s="21" t="s">
+    <row r="51" spans="1:4">
+      <c r="C51" s="58" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="C52" s="21" t="s">
+    <row r="52" spans="1:4">
+      <c r="C52" s="58" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="C53" s="21" t="s">
+    <row r="53" spans="1:4">
+      <c r="C53" s="58" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:4">
       <c r="A54" s="17">
         <v>46076</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="58" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:4">
       <c r="A55" s="17">
         <v>46077</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="58" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:4">
       <c r="A56" s="17">
         <v>46081</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="58" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:4">
       <c r="A57" s="17">
         <v>46082</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="58" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:4">
       <c r="A58" s="17">
         <v>46083</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="58" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="C59" t="s">
+    <row r="59" spans="1:4">
+      <c r="C59" s="58" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="C60" s="21" t="s">
+    <row r="60" spans="1:4">
+      <c r="C60" s="58" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="C61" t="s">
+    <row r="61" spans="1:4">
+      <c r="C61" s="58" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="C62" s="21" t="s">
+    <row r="62" spans="1:4">
+      <c r="C62" s="58" t="s">
         <v>102</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="43">
+        <v>46084</v>
+      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="20"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -1619,6 +1634,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1627,519 +1648,535 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:D58"/>
+  <dimension ref="B2:E60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" style="22" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="22" customWidth="1"/>
-    <col min="4" max="4" width="82.28515625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="82.28515625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="30">
-      <c r="B3" s="36">
+      <c r="B3" s="34">
         <v>46035</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="27">
         <v>2</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="31"/>
-      <c r="C4" s="29">
+      <c r="B4" s="29"/>
+      <c r="C4" s="27">
         <v>1</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="30">
-      <c r="B5" s="40">
+      <c r="B5" s="38">
         <v>46036</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>4</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="36">
+      <c r="B6" s="34">
         <v>46037</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="28">
         <v>4</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="29" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="29" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="29" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="27" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="29" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="27" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="35">
+      <c r="B11" s="33">
         <v>46039</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="29">
         <v>2</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="26" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="27">
+      <c r="B12" s="25">
         <v>46042</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="26">
         <v>0.5</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="27">
+      <c r="B13" s="25">
         <v>46043</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="26">
         <v>2</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="36">
+      <c r="B14" s="34">
         <v>46044</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="26">
         <v>2</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="26" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="36">
+      <c r="B15" s="34">
         <v>46046</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="27">
         <v>2</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="26" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="31"/>
-      <c r="C16" s="29">
+      <c r="B16" s="29"/>
+      <c r="C16" s="27">
         <v>2</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="26" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="35">
+      <c r="B17" s="33">
         <v>46047</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="26">
         <v>2</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="26" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="27">
+      <c r="B18" s="25">
         <v>46048</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="26">
         <v>1</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="36">
+      <c r="B19" s="34">
         <v>46049</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="26">
         <v>3</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="36">
+      <c r="B20" s="34">
         <v>46051</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="27">
         <v>4</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="31"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="28" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="26" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="40">
+      <c r="B22" s="38">
         <v>46055</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="28">
         <v>2</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="36">
+      <c r="B23" s="34">
         <v>46057</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="28">
         <v>3</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="29" t="s">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="27" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="27">
+      <c r="B25" s="25">
         <v>46058</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="26">
         <v>2</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="36">
+      <c r="B26" s="34">
         <v>46061</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="28">
         <v>4</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="27" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="29" t="s">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="27" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="36">
+      <c r="B28" s="34">
         <v>46062</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="28">
         <v>5</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="27" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="29" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="27" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="29" t="s">
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="27" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="29" t="s">
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="36">
+      <c r="B32" s="34">
         <v>46063</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="28">
         <v>5</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="29" t="s">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="36">
+      <c r="B34" s="34">
         <v>46065</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="28">
         <v>4</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="27" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="29" t="s">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="27" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="36">
+      <c r="B36" s="34">
         <v>46068</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="28">
         <v>5</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="27" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="29" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="27" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="40">
+      <c r="B38" s="38">
         <v>46070</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="21">
         <v>6</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="27" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="30">
-      <c r="B39" s="32"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="29" t="s">
+      <c r="B39" s="30"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="27" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="32"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="29" t="s">
+      <c r="B40" s="30"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="27" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="32"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="29" t="s">
+      <c r="B41" s="30"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="27" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="32"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="29" t="s">
+      <c r="B42" s="30"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="27" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="32"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="29" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="27" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="2:4">
-      <c r="B44" s="31"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="29" t="s">
+      <c r="B44" s="29"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="27" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="30">
-      <c r="B45" s="40">
+      <c r="B45" s="38">
         <v>46071</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="30">
         <v>6</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" s="26" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="46" spans="2:4">
-      <c r="B46" s="36">
+      <c r="B46" s="34">
         <v>46076</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="31">
         <v>8</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D46" s="27" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="30">
-      <c r="B47" s="32"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="29" t="s">
+      <c r="B47" s="30"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="27" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:4">
-      <c r="B48" s="38"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="37" t="s">
+      <c r="B48" s="36"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="2:4">
-      <c r="B49" s="39"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="37" t="s">
+    <row r="49" spans="2:5">
+      <c r="B49" s="37"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="30">
-      <c r="B50" s="52">
+    <row r="50" spans="2:5" ht="30">
+      <c r="B50" s="40">
         <v>46077</v>
       </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="54" t="s">
+      <c r="C50" s="41"/>
+      <c r="D50" s="42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="2:4" ht="30">
-      <c r="B51" s="52">
+    <row r="51" spans="2:5" ht="30">
+      <c r="B51" s="40">
         <v>46081</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="54" t="s">
+      <c r="C51" s="41"/>
+      <c r="D51" s="42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="2:4">
-      <c r="B52" s="52">
+    <row r="52" spans="2:5">
+      <c r="B52" s="40">
         <v>46082</v>
       </c>
-      <c r="C52" s="53"/>
-      <c r="D52" s="54" t="s">
+      <c r="C52" s="41"/>
+      <c r="D52" s="42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="2:4" ht="30">
-      <c r="B53" s="55">
+    <row r="53" spans="2:5" ht="30">
+      <c r="B53" s="43">
         <v>46083</v>
       </c>
-      <c r="C53" s="58"/>
-      <c r="D53" s="54" t="s">
+      <c r="C53" s="46"/>
+      <c r="D53" s="42" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="2:4" ht="30">
-      <c r="B54" s="56"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="54" t="s">
+    <row r="54" spans="2:5" ht="30">
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="2:4" ht="30">
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="54" t="s">
+    <row r="55" spans="2:5" ht="30">
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="42" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="2:4" ht="45">
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="54" t="s">
+    <row r="56" spans="2:5" ht="45">
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="42" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="2:4" ht="30">
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="54" t="s">
+    <row r="57" spans="2:5" ht="30">
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="2:4" ht="30">
-      <c r="B58" s="57"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="54" t="s">
+    <row r="58" spans="2:5" ht="30">
+      <c r="B58" s="45"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="42" t="s">
         <v>111</v>
+      </c>
+      <c r="E58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="43">
+        <v>46084</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="D60" s="20" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD354402-BD7B-4756-AB91-3FA51FF2EDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B350DE-E512-4029-8E9F-403918ABABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
   <si>
     <t>Date</t>
   </si>
@@ -413,6 +413,21 @@
   </si>
   <si>
     <t>fully integrated create demand request modal</t>
+  </si>
+  <si>
+    <t>Implemented inventory lot creation and stock validation logic, enabling farmers to dispatch products based on vendor demand requests.</t>
+  </si>
+  <si>
+    <t>Developed Vendor Dashboard features including Create Demand Request functionality and integration with backend API endpoints.</t>
+  </si>
+  <si>
+    <t>Implemented Incoming Dispatches view and Confirm Delivery workflow, updating dispatch delivery status and related demand request statuses.</t>
+  </si>
+  <si>
+    <t>Debugged and resolved full-stack integration issues including DTO mismatches, dropdown binding errors, missing API response fields, and EF Core query type issues.</t>
+  </si>
+  <si>
+    <t>Updated Vendor dashboard to support Create Demand Request modal and integrated it with VendorDemandRequestsController.cs and VendorDashboard.jsx.</t>
   </si>
 </sst>
 </file>
@@ -666,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -832,6 +847,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1648,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E60"/>
+  <dimension ref="B2:E65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -2166,18 +2187,50 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="2:5">
+    <row r="59" spans="2:5" ht="30">
       <c r="B59" s="43">
         <v>46084</v>
       </c>
-      <c r="D59" s="20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5">
-      <c r="D60" s="20" t="s">
-        <v>114</v>
-      </c>
+      <c r="C59" s="20">
+        <v>7</v>
+      </c>
+      <c r="D59" s="59" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="30">
+      <c r="D60" s="59" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="30">
+      <c r="B61" s="60"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" ht="30">
+      <c r="B62" s="60"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="30">
+      <c r="B63" s="60"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="60"/>
+      <c r="C64" s="59"/>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="60"/>
+      <c r="C65" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B350DE-E512-4029-8E9F-403918ABABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A43B1A-AADA-46CE-8C51-951E6526D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -428,6 +428,9 @@
   </si>
   <si>
     <t>Updated Vendor dashboard to support Create Demand Request modal and integrated it with VendorDemandRequestsController.cs and VendorDashboard.jsx.</t>
+  </si>
+  <si>
+    <t>created export csv back end controller for data extraction</t>
   </si>
 </sst>
 </file>
@@ -2227,6 +2230,9 @@
     <row r="64" spans="2:5">
       <c r="B64" s="60"/>
       <c r="C64" s="59"/>
+      <c r="D64" s="20" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="60"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A43B1A-AADA-46CE-8C51-951E6526D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55556894-C7B2-4EAB-B7E9-791EA015B23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -432,12 +432,15 @@
   <si>
     <t>created export csv back end controller for data extraction</t>
   </si>
+  <si>
+    <t>to do : build a simple moving-average demand forecasting module =&gt;later can replace/improve it with ML.NET without changing my whole app</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,8 +479,16 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,6 +498,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,7 +701,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -818,36 +835,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -855,6 +842,39 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1156,20 +1176,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="47">
+      <c r="A2" s="53">
         <v>46035</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="55">
         <v>2</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="58" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="48"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="52"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="59"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1236,20 +1256,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="47">
+      <c r="A12" s="53">
         <v>46039</v>
       </c>
-      <c r="B12" s="49">
+      <c r="B12" s="55">
         <v>2</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="58" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="54"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="60"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1332,10 +1352,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="47">
+      <c r="A22" s="53">
         <v>46049</v>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="55">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1343,17 +1363,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="56"/>
-      <c r="B23" s="50"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="56"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="47">
+      <c r="A24" s="53">
         <v>46051</v>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="55">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1361,8 +1381,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="56"/>
-      <c r="B25" s="50"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1379,10 +1399,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="47">
+      <c r="A27" s="53">
         <v>46057</v>
       </c>
-      <c r="B27" s="49">
+      <c r="B27" s="55">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1390,8 +1410,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="56"/>
-      <c r="B28" s="50"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -1430,29 +1450,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="55"/>
-      <c r="B32" s="53"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="55"/>
-      <c r="B33" s="53"/>
+      <c r="A33" s="51"/>
+      <c r="B33" s="52"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="55"/>
-      <c r="B34" s="53"/>
+      <c r="A34" s="51"/>
+      <c r="B34" s="52"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="55"/>
-      <c r="B35" s="53"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -1545,27 +1565,27 @@
       <c r="A49" s="17">
         <v>46071</v>
       </c>
-      <c r="C49" s="57" t="s">
+      <c r="C49" s="47" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="48" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="48" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="48" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="48" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1573,7 +1593,7 @@
       <c r="A54" s="17">
         <v>46076</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="48" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1581,7 +1601,7 @@
       <c r="A55" s="17">
         <v>46077</v>
       </c>
-      <c r="C55" s="58" t="s">
+      <c r="C55" s="48" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1589,7 +1609,7 @@
       <c r="A56" s="17">
         <v>46081</v>
       </c>
-      <c r="C56" s="58" t="s">
+      <c r="C56" s="48" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1597,7 +1617,7 @@
       <c r="A57" s="17">
         <v>46082</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="48" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1605,27 +1625,27 @@
       <c r="A58" s="17">
         <v>46083</v>
       </c>
-      <c r="C58" s="58" t="s">
+      <c r="C58" s="48" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="48" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="C60" s="58" t="s">
+      <c r="C60" s="48" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="C61" s="58" t="s">
+      <c r="C61" s="48" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="C62" s="58" t="s">
+      <c r="C62" s="48" t="s">
         <v>102</v>
       </c>
       <c r="D62" t="s">
@@ -1650,6 +1670,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -1658,12 +1684,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2197,46 +2217,51 @@
       <c r="C59" s="20">
         <v>7</v>
       </c>
-      <c r="D59" s="59" t="s">
+      <c r="D59" s="49" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="30">
-      <c r="D60" s="59" t="s">
+      <c r="D60" s="49" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="30">
-      <c r="B61" s="60"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59" t="s">
+      <c r="B61" s="50"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="49" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="30">
-      <c r="B62" s="60"/>
-      <c r="C62" s="59"/>
-      <c r="D62" s="59" t="s">
+      <c r="B62" s="50"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="30">
-      <c r="B63" s="60"/>
-      <c r="C63" s="59"/>
-      <c r="D63" s="59" t="s">
+      <c r="B63" s="50"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="60"/>
-      <c r="C64" s="59"/>
+      <c r="B64" s="50"/>
+      <c r="C64" s="49"/>
       <c r="D64" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="2:3">
-      <c r="B65" s="60"/>
-      <c r="C65" s="59"/>
+    <row r="65" spans="2:4">
+      <c r="B65" s="50">
+        <v>46088</v>
+      </c>
+      <c r="C65" s="49"/>
+      <c r="D65" s="61" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55556894-C7B2-4EAB-B7E9-791EA015B23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDD923B-E32A-45A8-9D7E-6A9A70199F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="123">
   <si>
     <t>Date</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>to do : build a simple moving-average demand forecasting module =&gt;later can replace/improve it with ML.NET without changing my whole app</t>
+  </si>
+  <si>
+    <t>1. Create the DemandForecast model</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E65"/>
+  <dimension ref="B2:E66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -2263,6 +2266,11 @@
         <v>121</v>
       </c>
     </row>
+    <row r="66" spans="2:4">
+      <c r="D66" s="20" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDD923B-E32A-45A8-9D7E-6A9A70199F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F746C-21AD-4C49-8774-29638436285B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
   <si>
     <t>Date</t>
   </si>
@@ -433,10 +433,35 @@
     <t>created export csv back end controller for data extraction</t>
   </si>
   <si>
-    <t>to do : build a simple moving-average demand forecasting module =&gt;later can replace/improve it with ML.NET without changing my whole app</t>
-  </si>
-  <si>
     <t>1. Create the DemandForecast model</t>
+  </si>
+  <si>
+    <t>forecasting baseline module is complete</t>
+  </si>
+  <si>
+    <t>Implementation Plan : Create Optimization Result Table,</t>
+  </si>
+  <si>
+    <t>Create Optimization Result Table</t>
+  </si>
+  <si>
+    <t>DispatchOptimizationService.cs : DispatchOptimizationService.cs</t>
+  </si>
+  <si>
+    <t>Logic:
+Read forecast demand
+Read farmer inventory
+Match inventory to demand
+Allocate quantities</t>
+  </si>
+  <si>
+    <t>Create Optimization API</t>
+  </si>
+  <si>
+    <t>Relationship Score Tracking</t>
+  </si>
+  <si>
+    <t>started with  build a simple moving-average demand forecasting module =&gt;later can replace/improve it with ML.NET without changing my whole app</t>
   </si>
 </sst>
 </file>
@@ -704,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -846,37 +871,43 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1179,20 +1210,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="53">
+      <c r="A2" s="52">
         <v>46035</v>
       </c>
-      <c r="B2" s="55">
+      <c r="B2" s="54">
         <v>2</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="56" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="59"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="57"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1259,20 +1290,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="53">
+      <c r="A12" s="52">
         <v>46039</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="54">
         <v>2</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="56" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="57"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="60"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1355,10 +1386,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="53">
+      <c r="A22" s="52">
         <v>46049</v>
       </c>
-      <c r="B22" s="55">
+      <c r="B22" s="54">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1366,17 +1397,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="54"/>
-      <c r="B23" s="56"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="55"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="53">
+      <c r="A24" s="52">
         <v>46051</v>
       </c>
-      <c r="B24" s="55">
+      <c r="B24" s="54">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1384,8 +1415,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="54"/>
-      <c r="B25" s="56"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="55"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1402,10 +1433,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="53">
+      <c r="A27" s="52">
         <v>46057</v>
       </c>
-      <c r="B27" s="55">
+      <c r="B27" s="54">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1413,8 +1444,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="54"/>
-      <c r="B28" s="56"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="55"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -1453,29 +1484,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="52"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="51"/>
-      <c r="B33" s="52"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="58"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="51"/>
-      <c r="B34" s="52"/>
+      <c r="A34" s="60"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="51"/>
-      <c r="B35" s="52"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -1673,12 +1704,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -1687,6 +1712,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1695,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E66"/>
+  <dimension ref="B2:E73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -2262,13 +2293,48 @@
         <v>46088</v>
       </c>
       <c r="C65" s="49"/>
-      <c r="D65" s="61" t="s">
-        <v>121</v>
+      <c r="D65" s="51" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="D66" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="D67" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="D68" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="D69" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="D70" s="63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="135">
+      <c r="D71" s="62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="D72" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="D73" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F746C-21AD-4C49-8774-29638436285B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410C761E-ED3C-498E-8672-8637273DA6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t>started with  build a simple moving-average demand forecasting module =&gt;later can replace/improve it with ML.NET without changing my whole app</t>
+  </si>
+  <si>
+    <t>optimization module</t>
+  </si>
+  <si>
+    <t>research on optimization module generation</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -874,10 +880,22 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -886,28 +904,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1210,20 +1219,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="52">
+      <c r="A2" s="56">
         <v>46035</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B2" s="58">
         <v>2</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="61" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="57"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="62"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1290,20 +1299,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="52">
+      <c r="A12" s="56">
         <v>46039</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="58">
         <v>2</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="61" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="63"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1386,10 +1395,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="52">
+      <c r="A22" s="56">
         <v>46049</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="58">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1397,17 +1406,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="61"/>
-      <c r="B23" s="55"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="52">
+      <c r="A24" s="56">
         <v>46051</v>
       </c>
-      <c r="B24" s="54">
+      <c r="B24" s="58">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1415,8 +1424,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="61"/>
-      <c r="B25" s="55"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1433,10 +1442,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="52">
+      <c r="A27" s="56">
         <v>46057</v>
       </c>
-      <c r="B27" s="54">
+      <c r="B27" s="58">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1444,8 +1453,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="61"/>
-      <c r="B28" s="55"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -1484,29 +1493,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="60"/>
-      <c r="B32" s="58"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="60"/>
-      <c r="B33" s="58"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="60"/>
-      <c r="B34" s="58"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="55"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="60"/>
-      <c r="B35" s="58"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="55"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -1704,6 +1713,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -1712,12 +1727,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1726,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E73"/>
+  <dimension ref="B2:E75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -2318,12 +2327,12 @@
       </c>
     </row>
     <row r="70" spans="2:4">
-      <c r="D70" s="63" t="s">
+      <c r="D70" s="53" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="71" spans="2:4" ht="135">
-      <c r="D71" s="62" t="s">
+      <c r="D71" s="52" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2335,6 +2344,22 @@
     <row r="73" spans="2:4">
       <c r="D73" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="64">
+        <v>46089</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="64">
+        <v>46090</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410C761E-ED3C-498E-8672-8637273DA6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4841A618-8108-4DCA-9AA4-41E4F636B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="145">
   <si>
     <t>Date</t>
   </si>
@@ -467,7 +467,90 @@
     <t>optimization module</t>
   </si>
   <si>
-    <t>research on optimization module generation</t>
+    <t>research on optimization module generation :Based on forecasted demand and available inventory, which farmer should dispatch how much product to which vendor? =&gt; Based on forecasted demand and available inventory, which farmer should dispatch how much product to which vendor?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">store/update relationship score between </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Farmer ↔ Vendor</t>
+    </r>
+  </si>
+  <si>
+    <t>update scores automatically when a dispatch becomes:(Delivered,Cancelled)</t>
+  </si>
+  <si>
+    <t>compute score from measurable factors(On-time delivery rate
+Fulfillment rate
+Cancellation rate)</t>
+  </si>
+  <si>
+    <t>expose API to view scores</t>
+  </si>
+  <si>
+    <t>add/update:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. RelationshipStat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> model</t>
+    </r>
+  </si>
+  <si>
+    <t>2. RelationshipScoreRowDto</t>
+  </si>
+  <si>
+    <t>3. RelationshipScoreService</t>
+  </si>
+  <si>
+    <t>4. RelationshipStatsController</t>
+  </si>
+  <si>
+    <t>5. integrate score update into:</t>
+  </si>
+  <si>
+    <r>
+      <t>VendorDispatchesController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> confirm delivery</t>
+    </r>
+  </si>
+  <si>
+    <t>optional cancel/update endpoints</t>
+  </si>
+  <si>
+    <t>TO DO : generate frontend view for below endpoint:                                                                          GET /api/forecasts
+POST /api/forecasts/generate
+GET /api/optimization/plans
+POST /api/optimization/run
+GET /api/relationshipstats
+GET /api/relationshipstats/by-pair?</t>
   </si>
 </sst>
 </file>
@@ -735,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -918,6 +1001,21 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1735,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E75"/>
+  <dimension ref="B2:E100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -2362,6 +2460,97 @@
         <v>130</v>
       </c>
     </row>
+    <row r="77" spans="2:4">
+      <c r="D77" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="D78" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="D79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="75">
+      <c r="D80" s="19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4">
+      <c r="D81" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4">
+      <c r="D82" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="65"/>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="66" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="65"/>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="66" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="65"/>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="66" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="65"/>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="66" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="65"/>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="65"/>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="68" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="4:4">
+      <c r="D95" s="67"/>
+    </row>
+    <row r="96" spans="4:4">
+      <c r="D96" s="67" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" ht="180">
+      <c r="D100" s="69" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4841A618-8108-4DCA-9AA4-41E4F636B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFEA4A9-0AB6-48EA-8DDC-E7CEFF7F6E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="182">
   <si>
     <t>Date</t>
   </si>
@@ -552,12 +554,352 @@
 GET /api/relationshipstats
 GET /api/relationshipstats/by-pair?</t>
   </si>
+  <si>
+    <t>Implemented inventory lot creation and stock validation logic to support dispatch planning from farmer inventory against vendor demand requests.</t>
+  </si>
+  <si>
+    <t>Developed Vendor Dashboard functionality for Create Demand Request and integrated frontend actions with backend API endpoints.</t>
+  </si>
+  <si>
+    <t>Implemented Incoming Dispatches view and Confirm Delivery workflow, including updates to dispatch delivery status and related demand request status.</t>
+  </si>
+  <si>
+    <t>Resolved full-stack integration issues involving DTO mismatches, dropdown binding problems, missing response fields, and EF Core query typing issues.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorDashboard.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and integrated modal-based demand request creation with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorDemandRequestsController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Added backend support for CSV/data extraction to prepare for forecasting and experimental analysis.</t>
+  </si>
+  <si>
+    <t>Began implementation of a moving-average demand forecasting baseline in .NET as the first forecasting approach for the research module.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Created the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> model, supporting DTOs, and required database updates for forecast storage.</t>
+    </r>
+  </si>
+  <si>
+    <t>Completed baseline forecasting workflow and tested forecast generation successfully through API endpoints.</t>
+  </si>
+  <si>
+    <t>Designed the optimization module structure by defining the optimization result table and dispatch recommendation flow.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DispatchOptimizationService.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using greedy baseline allocation logic based on forecast demand and available farmer inventory.</t>
+    </r>
+  </si>
+  <si>
+    <t>Created optimization API endpoints for generating and retrieving recommended dispatch plans.</t>
+  </si>
+  <si>
+    <t>Conducted research and design for the optimization component, focusing on demand-driven farmer-to-vendor dispatch decision logic using forecast and inventory data.</t>
+  </si>
+  <si>
+    <t>Refined the optimization formulation to support the research novelty component of the project.</t>
+  </si>
+  <si>
+    <t>Implemented the optimization module and connected it with forecast and inventory data to generate recommended dispatch plans.</t>
+  </si>
+  <si>
+    <t>Implemented relationship score tracking between Farmer and Vendor pairs based on dispatch outcomes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added automatic score updates for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Delivered</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Cancelled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dispatch events.</t>
+    </r>
+  </si>
+  <si>
+    <t>Computed relationship score using measurable factors including on-time delivery rate, fulfillment rate, and cancellation rate.</t>
+  </si>
+  <si>
+    <t>Exposed backend API endpoints for viewing relationship statistics.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added and updated files required for relationship scoring, including </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RelationshipStat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RelationshipScoreRowDto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RelationshipScoreService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RelationshipStatsController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated score update logic into </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorDispatchesController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> confirm delivery flow and outlined remaining frontend analytics views for forecast, optimization, and relationship endpoints.</t>
+    </r>
+  </si>
+  <si>
+    <t>Work Completed</t>
+  </si>
+  <si>
+    <t>Details / Description</t>
+  </si>
+  <si>
+    <t>Vendor-side functional enhancements</t>
+  </si>
+  <si>
+    <t>Implemented inventory lot creation and stock validation, enabling farmers to dispatch products based on vendor demand requests. Integrated Create Demand Request UI with backend APIs. Built Incoming Dispatches view and the Confirm Delivery workflow, which updates dispatch and demand request statuses automatically. Fixed multiple integration issues including DTO mismatches, binding errors, missing fields, and EF Core query problems. Added backend CSV/data export features.</t>
+  </si>
+  <si>
+    <t>Baseline demand forecasting module</t>
+  </si>
+  <si>
+    <t>Developed a simple moving‑average forecasting engine in .NET. Added logic to generate product-level demand predictions and store them in the database for later research and evaluation.</t>
+  </si>
+  <si>
+    <t>March 7–8</t>
+  </si>
+  <si>
+    <t>Dispatch optimization module</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Designed and implemented a greedy allocation optimization technique to match farmer inventory with forecasted vendor demand. Created the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DispatchOptimizationService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, integrated it with inventory and forecast data, and added API endpoints for generating and retrieving optimized dispatch plans.</t>
+    </r>
+  </si>
+  <si>
+    <t>Optimization research &amp; design</t>
+  </si>
+  <si>
+    <t>Conducted research on allocation strategies to determine how forecasted demand and inventory should drive decisions on which farmer supplies which vendor and in what quantity. Refined the optimization workflow based on analysis.</t>
+  </si>
+  <si>
+    <t>Relationship scoring module</t>
+  </si>
+  <si>
+    <t>Implemented a scoring model that evaluates farmer–vendor collaboration based on fulfillment rate, on-time delivery, and cancellation rate. Added models, DTOs, and API endpoints for viewing relationship statistics. Integrated automatic score recalculation into the delivery confirmation workflow so that scores update whenever a dispatch is delivered or cancelled.</t>
+  </si>
+  <si>
+    <t>Full-stack integration &amp; research preparation</t>
+  </si>
+  <si>
+    <t>Resolved backend–frontend mismatches across DTOs, route models, and API responses. Ensured that forecasting, optimization, and scoring modules are fully operational for the upcoming experimental evaluation phase. Added database logging and support structures for future analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March 3–9 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,6 +946,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -625,7 +980,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -814,11 +1169,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1016,6 +1417,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2555,4 +2995,293 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
+  <dimension ref="B2:D23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="71.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B3" s="76">
+        <v>46084</v>
+      </c>
+      <c r="C3" s="70">
+        <v>6</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B5" s="75"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="41" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B6" s="76">
+        <v>46086</v>
+      </c>
+      <c r="C6" s="73">
+        <v>5</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B9" s="76">
+        <v>46088</v>
+      </c>
+      <c r="C9" s="73">
+        <v>6</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="41" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="41" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B15" s="76">
+        <v>46089</v>
+      </c>
+      <c r="C15" s="73">
+        <v>3</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B17" s="76">
+        <v>46090</v>
+      </c>
+      <c r="C17" s="73">
+        <v>6</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="41" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="41" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="38.25" customHeight="1">
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="41" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F000D01-920E-4EFE-A851-9564F79E29F6}">
+  <dimension ref="B1:D8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="44.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B2" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="82" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="231.75" thickBot="1">
+      <c r="B3" s="79">
+        <v>46084</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="99.75" thickBot="1">
+      <c r="B4" s="79">
+        <v>46088</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="149.25" thickBot="1">
+      <c r="B5" s="81" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="116.25" thickBot="1">
+      <c r="B6" s="79">
+        <v>46089</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="182.25" thickBot="1">
+      <c r="B7" s="79">
+        <v>46090</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="80" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="132.75" thickBot="1">
+      <c r="B8" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Desktop\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFEA4A9-0AB6-48EA-8DDC-E7CEFF7F6E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C72A2D5-AE24-4371-BA78-103EFD2C69BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="184">
   <si>
     <t>Date</t>
   </si>
@@ -893,6 +893,12 @@
   </si>
   <si>
     <t xml:space="preserve">March 3–9 </t>
+  </si>
+  <si>
+    <t>individual checking</t>
+  </si>
+  <si>
+    <t>changing research baseline model to ML related model which focus on ML.NET’s forecasting task -provide more in detail</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1370,92 +1376,95 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1757,20 +1766,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="56">
+      <c r="A2" s="73">
         <v>46035</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="75">
         <v>2</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="77" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="62"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="78"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1837,20 +1846,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="56">
+      <c r="A12" s="73">
         <v>46039</v>
       </c>
-      <c r="B12" s="58">
+      <c r="B12" s="75">
         <v>2</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="77" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="60"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="63"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1933,10 +1942,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="56">
+      <c r="A22" s="73">
         <v>46049</v>
       </c>
-      <c r="B22" s="58">
+      <c r="B22" s="75">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1944,17 +1953,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="57"/>
-      <c r="B23" s="59"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="76"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="56">
+      <c r="A24" s="73">
         <v>46051</v>
       </c>
-      <c r="B24" s="58">
+      <c r="B24" s="75">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1962,8 +1971,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="57"/>
-      <c r="B25" s="59"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1980,10 +1989,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="56">
+      <c r="A27" s="73">
         <v>46057</v>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="75">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1991,8 +2000,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="57"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -2031,29 +2040,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="54"/>
-      <c r="B32" s="55"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="54"/>
-      <c r="B33" s="55"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="54"/>
-      <c r="B34" s="55"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="79"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="54"/>
-      <c r="B35" s="55"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="79"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -2251,12 +2260,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -2265,6 +2268,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2885,7 +2894,7 @@
       </c>
     </row>
     <row r="74" spans="2:4">
-      <c r="B74" s="64">
+      <c r="B74" s="54">
         <v>46089</v>
       </c>
       <c r="D74" s="20" t="s">
@@ -2893,7 +2902,7 @@
       </c>
     </row>
     <row r="75" spans="2:4">
-      <c r="B75" s="64">
+      <c r="B75" s="54">
         <v>46090</v>
       </c>
       <c r="D75" s="20" t="s">
@@ -2931,63 +2940,63 @@
       </c>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="65"/>
+      <c r="D83" s="55"/>
     </row>
     <row r="84" spans="4:4">
-      <c r="D84" s="66" t="s">
+      <c r="D84" s="56" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="85" spans="4:4">
-      <c r="D85" s="65"/>
+      <c r="D85" s="55"/>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="66" t="s">
+      <c r="D86" s="56" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="87" spans="4:4">
-      <c r="D87" s="65"/>
+      <c r="D87" s="55"/>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="66" t="s">
+      <c r="D88" s="56" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="89" spans="4:4">
-      <c r="D89" s="65"/>
+      <c r="D89" s="55"/>
     </row>
     <row r="90" spans="4:4">
-      <c r="D90" s="66" t="s">
+      <c r="D90" s="56" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="91" spans="4:4">
-      <c r="D91" s="65"/>
+      <c r="D91" s="55"/>
     </row>
     <row r="92" spans="4:4">
-      <c r="D92" s="65" t="s">
+      <c r="D92" s="55" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="93" spans="4:4">
-      <c r="D93" s="65"/>
+      <c r="D93" s="55"/>
     </row>
     <row r="94" spans="4:4">
-      <c r="D94" s="68" t="s">
+      <c r="D94" s="58" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="95" spans="4:4">
-      <c r="D95" s="67"/>
+      <c r="D95" s="57"/>
     </row>
     <row r="96" spans="4:4">
-      <c r="D96" s="67" t="s">
+      <c r="D96" s="57" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="4:4" ht="180">
-      <c r="D100" s="69" t="s">
+      <c r="D100" s="59" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2999,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
-  <dimension ref="B2:D23"/>
+  <dimension ref="B2:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -3008,21 +3017,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="67" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B3" s="76">
+      <c r="B3" s="66">
         <v>46084</v>
       </c>
-      <c r="C3" s="70">
+      <c r="C3" s="60">
         <v>6</v>
       </c>
       <c r="D3" s="41" t="s">
@@ -3030,24 +3039,24 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B4" s="74"/>
-      <c r="C4" s="71"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="61"/>
       <c r="D4" s="41" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B5" s="75"/>
-      <c r="C5" s="72"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="62"/>
       <c r="D5" s="41" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B6" s="76">
+      <c r="B6" s="66">
         <v>46086</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="63">
         <v>5</v>
       </c>
       <c r="D6" s="41" t="s">
@@ -3055,24 +3064,24 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="41" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="41" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B9" s="76">
+      <c r="B9" s="66">
         <v>46088</v>
       </c>
-      <c r="C9" s="73">
+      <c r="C9" s="63">
         <v>6</v>
       </c>
       <c r="D9" s="41" t="s">
@@ -3080,45 +3089,45 @@
       </c>
     </row>
     <row r="10" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="41" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="41" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="41" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="41" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="41" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B15" s="76">
+      <c r="B15" s="66">
         <v>46089</v>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="63">
         <v>3</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -3126,17 +3135,17 @@
       </c>
     </row>
     <row r="16" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="41" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B17" s="76">
+      <c r="B17" s="66">
         <v>46090</v>
       </c>
-      <c r="C17" s="73">
+      <c r="C17" s="63">
         <v>6</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -3144,45 +3153,61 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="41" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="41" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="41" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="41" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="41" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="38.25" customHeight="1">
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
       <c r="D23" s="41" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="17">
+        <v>46091</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="30">
+      <c r="D25" s="83" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3193,7 +3218,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F000D01-920E-4EFE-A851-9564F79E29F6}">
-  <dimension ref="B1:D8"/>
+  <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -3204,80 +3229,85 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:4" ht="17.25" thickBot="1">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="72" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="231.75" thickBot="1">
-      <c r="B3" s="79">
+      <c r="B3" s="69">
         <v>46084</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="70" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="99.75" thickBot="1">
-      <c r="B4" s="79">
+      <c r="B4" s="69">
         <v>46088</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="70" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="D4" s="70" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="149.25" thickBot="1">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="71" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="70" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="80" t="s">
+      <c r="D5" s="70" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="116.25" thickBot="1">
-      <c r="B6" s="79">
+      <c r="B6" s="69">
         <v>46089</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="70" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="70" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="182.25" thickBot="1">
-      <c r="B7" s="79">
+      <c r="B7" s="69">
         <v>46090</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="70" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="80" t="s">
+      <c r="D7" s="70" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="132.75" thickBot="1">
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="70" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="70" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="17">
+        <v>46091</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C72A2D5-AE24-4371-BA78-103EFD2C69BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE55D4FA-EF8C-448F-B03D-970E23721EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="186">
   <si>
     <t>Date</t>
   </si>
@@ -899,6 +899,12 @@
   </si>
   <si>
     <t>changing research baseline model to ML related model which focus on ML.NET’s forecasting task -provide more in detail</t>
+  </si>
+  <si>
+    <t>to do</t>
+  </si>
+  <si>
+    <t>to do : add forecast charts</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1433,39 +1439,40 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1766,20 +1773,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="73">
+      <c r="A2" s="76">
         <v>46035</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="78">
         <v>2</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="81" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="78"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="82"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -1846,20 +1853,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="73">
+      <c r="A12" s="76">
         <v>46039</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="78">
         <v>2</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="81" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="83"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -1942,10 +1949,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="73">
+      <c r="A22" s="76">
         <v>46049</v>
       </c>
-      <c r="B22" s="75">
+      <c r="B22" s="78">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1953,17 +1960,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="82"/>
-      <c r="B23" s="76"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="73">
+      <c r="A24" s="76">
         <v>46051</v>
       </c>
-      <c r="B24" s="75">
+      <c r="B24" s="78">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1971,8 +1978,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="82"/>
-      <c r="B25" s="76"/>
+      <c r="A25" s="77"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -1989,10 +1996,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="73">
+      <c r="A27" s="76">
         <v>46057</v>
       </c>
-      <c r="B27" s="75">
+      <c r="B27" s="78">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -2000,8 +2007,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="82"/>
-      <c r="B28" s="76"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -2040,29 +2047,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="81"/>
-      <c r="B32" s="79"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="75"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="81"/>
-      <c r="B33" s="79"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="75"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="81"/>
-      <c r="B34" s="79"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="81"/>
-      <c r="B35" s="79"/>
+      <c r="A35" s="74"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -2260,6 +2267,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -2268,12 +2281,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2282,7 +2289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36D1A51-7B38-4D49-AACB-A85A6A2358FE}">
-  <dimension ref="B2:E100"/>
+  <dimension ref="B2:E107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="7.7109375" style="20" customWidth="1"/>
@@ -3000,6 +3007,11 @@
         <v>144</v>
       </c>
     </row>
+    <row r="107" spans="4:4">
+      <c r="D107" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3008,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
-  <dimension ref="B2:D25"/>
+  <dimension ref="B2:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -3201,13 +3213,18 @@
       <c r="C24">
         <v>6</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="73" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="D25" s="83" t="s">
+      <c r="D25" s="73" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="D31" s="84" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE55D4FA-EF8C-448F-B03D-970E23721EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8BBC11-7E71-4FCC-AD52-B403BD77B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8BBC11-7E71-4FCC-AD52-B403BD77B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36138B6-28A2-4EB7-9ECC-E14F9FBA6DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="205">
   <si>
     <t>Date</t>
   </si>
@@ -898,13 +899,586 @@
     <t>individual checking</t>
   </si>
   <si>
-    <t>changing research baseline model to ML related model which focus on ML.NET’s forecasting task -provide more in detail</t>
-  </si>
-  <si>
     <t>to do</t>
   </si>
   <si>
-    <t>to do : add forecast charts</t>
+    <t>changing research baseline model to ML related model which focus on ML.NET’s forecasting tas</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Researched machine learning–based forecasting approaches and identified </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML.NET SSA (Singular Spectrum Analysis) time series forecasting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as a more suitable ML-driven model for demand prediction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Studied ML.NET forecasting pipeline structure including </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SSA training window, horizon prediction, model retraining, and demand sequence preparation from historical demand request data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated research direction by replacing the baseline-only approach with an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML-focused forecasting implementation using ML.NET TimeSeries API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and refactored the forecasting workflow in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecastService.cs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Studied ML.NET forecasting pipeline structure including </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SSA training window, horizon prediction, model retraining, and demand sequence preparation from historical demand request data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, preparing the implementation structure for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLDemandForecastEngine.cs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refactored forecasting architecture to support </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiple forecasting models (Moving Average + ML.NET SSA)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and updated related models including </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecast.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>GenerateForecastDto.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecastRowDto.cs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML.NET forecasting engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> inside the backend service layer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Created </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLDemandForecastEngine.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to train ML.NET models using historical demand request quantities stored in the database.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented time-series training pipeline using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLContext and SSA forecasting trainer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to predict future vendor demand quantities inside </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLDemandForecastEngine.cs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated ML forecast generation into the existing forecasting workflow by updating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecastService.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> so prediction results can be stored in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> table</t>
+    </r>
+  </si>
+  <si>
+    <t>Tested the ML.NET forecasting pipeline using historical demand request data inserted into the database and validated forecasting output.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verified training data extraction, forecast horizon configuration, and prediction output structure in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLDemandForecastEngine.cs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Added model identification field (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ModelName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) to distinguish forecast outputs from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MovingAverage vs MLNET_SSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> models and updated related structures in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecast.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecastRowDto.cs</t>
+    </r>
+  </si>
+  <si>
+    <t>Developed backend API endpoints to support ML forecasting execution and retrieval through the forecasting module</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented API logic in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ForecastController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for generating ML forecasts and storing prediction results in the database.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ensured compatibility between backend forecasting APIs and frontend analytics components by updating request/response DTOs such as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>GenerateForecastDto.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DemandForecastRowDto.cs</t>
+    </r>
+  </si>
+  <si>
+    <t>Developed frontend analytics dashboard for displaying forecasting results and model comparison functionality.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vendor Forecast Analytics page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorForecast.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> including forecast generation form and model comparison module between Moving Average and ML.NET models.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated forecasting APIs with React frontend components using secure token-based authentication through </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>forecastApi.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and existing route protection logic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>forecast visualization charts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to the analytics dashboard to represent demand history and forecast trends visually.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented chart component </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ForecastLineChart.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to display historical demand data alongside forecast predictions.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1231,7 +1805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1472,7 +2046,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3009,7 +3582,7 @@
     </row>
     <row r="107" spans="4:4">
       <c r="D107" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3019,13 +3592,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86F43F-C884-40ED-8D9B-040E7647202D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
-  <dimension ref="B2:D31"/>
+  <dimension ref="B2:D45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="71.28515625" customWidth="1"/>
+    <col min="4" max="4" width="71.28515625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -3219,12 +3801,131 @@
     </row>
     <row r="25" spans="2:4" ht="30">
       <c r="D25" s="73" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="45">
+      <c r="D26" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="45">
+      <c r="D27" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="60">
+      <c r="D28" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="45">
+      <c r="D29" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="45">
+      <c r="D30" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="2:4">
-      <c r="D31" s="84" t="s">
-        <v>185</v>
+      <c r="B31" s="17">
+        <v>46092</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="D32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="D34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="17">
+        <v>46093</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="D36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="17">
+        <v>46094</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="D39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="D40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="D41" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="17">
+        <v>46097</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="D43" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="D44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="D45" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3233,7 +3934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F000D01-920E-4EFE-A851-9564F79E29F6}">
   <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36138B6-28A2-4EB7-9ECC-E14F9FBA6DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6424042-19FD-4AFA-B16C-E0C8343A1259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1 (2)" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId4"/>
+    <sheet name="report4" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
+    <sheet name="report4 value added" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="211">
   <si>
     <t>Date</t>
   </si>
@@ -1480,12 +1482,167 @@
       <t xml:space="preserve"> to display historical demand data alongside forecast predictions.</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated chart component into both analytics pages </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorForecast.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FarmerForecast.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to provide graphical interpretation of forecasting results.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Began implementation of a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>real-time communication feature</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> between farmers and vendors within the FarmVendor system.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Designed the chat module architecture and developed frontend messaging components </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FarmerChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated authentication logic in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Login.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to store </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in localStorage to support message sender identification for chat communication.</t>
+    </r>
+  </si>
+  <si>
+    <t>Prepared frontend system structure for integrating backend chat APIs and enabling future real-time messaging functionality between farmers and vendors.</t>
+  </si>
+  <si>
+    <t>Completed Progress report 4 and uploaded to blackboard and checked in to github repository.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1545,8 +1702,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1565,8 +1729,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1801,11 +1971,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2045,6 +2228,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3592,17 +3796,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86F43F-C884-40ED-8D9B-040E7647202D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
-  <dimension ref="B2:D45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEEF419-CB03-460C-8DC3-1B7F122CFE14}">
+  <dimension ref="B2:D51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -3829,103 +4024,133 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
+    <row r="31" spans="2:4" ht="30">
       <c r="B31" s="17">
         <v>46092</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
-      <c r="D32" t="s">
+    <row r="32" spans="2:4" ht="30">
+      <c r="D32" s="19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="D33" t="s">
+    <row r="33" spans="2:4" ht="43.5">
+      <c r="D33" s="19" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="D34" t="s">
+    <row r="34" spans="2:4" ht="45">
+      <c r="D34" s="19" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="17">
         <v>46093</v>
       </c>
       <c r="C35">
         <v>6</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="19" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="D36" t="s">
+    <row r="36" spans="2:4" ht="30">
+      <c r="D36" s="19" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="D37" t="s">
+    <row r="37" spans="2:4" ht="45">
+      <c r="D37" s="19" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
+    <row r="38" spans="2:4" ht="30">
       <c r="B38" s="17">
         <v>46094</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
-      <c r="D39" t="s">
+    <row r="39" spans="2:4" ht="30">
+      <c r="D39" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
-      <c r="D40" t="s">
+    <row r="40" spans="2:4" ht="45">
+      <c r="D40" s="19" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="D41" t="s">
+    <row r="41" spans="2:4" ht="30">
+      <c r="D41" s="19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:4" ht="45">
       <c r="B42" s="17">
         <v>46097</v>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="19" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
-      <c r="D43" t="s">
+    <row r="43" spans="2:4" ht="45">
+      <c r="D43" s="19" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
-      <c r="D44" t="s">
+    <row r="44" spans="2:4" ht="30">
+      <c r="D44" s="19" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
-      <c r="D45" t="s">
+    <row r="45" spans="2:4" ht="30">
+      <c r="D45" s="19" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="30">
+      <c r="D46" s="49" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="30">
+      <c r="D47" s="49" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="30">
+      <c r="D48" s="49" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" ht="30">
+      <c r="D49" s="49" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" ht="45">
+      <c r="D50" s="49" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" ht="30">
+      <c r="D51" s="19" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3934,7 +4159,271 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86F43F-C884-40ED-8D9B-040E7647202D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
+  <dimension ref="B2:D30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="71.28515625" style="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="86">
+        <v>46091</v>
+      </c>
+      <c r="C3" s="87">
+        <v>6</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="30">
+      <c r="B4" s="86"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="84" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="45">
+      <c r="B5" s="86"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="85" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="45">
+      <c r="B6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="85" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="60">
+      <c r="B7" s="86"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="85" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="45">
+      <c r="B8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="85" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="45">
+      <c r="B9" s="86"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="85" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="30">
+      <c r="B10" s="88">
+        <v>46092</v>
+      </c>
+      <c r="C10" s="87">
+        <v>4</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="30">
+      <c r="B11" s="88"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="85" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="43.5">
+      <c r="B12" s="88"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="85" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="45">
+      <c r="B13" s="88"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="85" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="30">
+      <c r="B14" s="88">
+        <v>46093</v>
+      </c>
+      <c r="C14" s="87">
+        <v>6</v>
+      </c>
+      <c r="D14" s="85" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="30">
+      <c r="B15" s="88"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="85" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="45">
+      <c r="B16" s="88"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="85" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="30">
+      <c r="B17" s="88">
+        <v>46094</v>
+      </c>
+      <c r="C17" s="87">
+        <v>4</v>
+      </c>
+      <c r="D17" s="85" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="30">
+      <c r="B18" s="88"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="85" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="45">
+      <c r="B19" s="88"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="85" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="30">
+      <c r="B20" s="88"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="85" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="45">
+      <c r="B21" s="88">
+        <v>46097</v>
+      </c>
+      <c r="C21" s="87">
+        <v>5</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="45">
+      <c r="B22" s="88"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="85" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="30">
+      <c r="B23" s="88"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="85" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="30">
+      <c r="B24" s="88"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="30">
+      <c r="B25" s="88"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="30">
+      <c r="B26" s="88"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="41" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="30">
+      <c r="B27" s="88"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="30">
+      <c r="B28" s="88"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="41" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="45">
+      <c r="B29" s="88"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="30">
+      <c r="B30" s="88"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="85" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B30"/>
+    <mergeCell ref="C21:C30"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C3:C9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F000D01-920E-4EFE-A851-9564F79E29F6}">
   <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4032,4 +4521,32 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
+  <dimension ref="B1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="82" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B2" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="90" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6424042-19FD-4AFA-B16C-E0C8343A1259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B741FB-5592-4292-93B7-86CF5BD5141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="225">
   <si>
     <t>Date</t>
   </si>
@@ -1637,12 +1637,146 @@
   <si>
     <t>Completed Progress report 4 and uploaded to blackboard and checked in to github repository.</t>
   </si>
+  <si>
+    <t>Forecasting model research and improvement</t>
+  </si>
+  <si>
+    <t>ML forecasting engine implementation</t>
+  </si>
+  <si>
+    <t>Forecasting data validation and testing</t>
+  </si>
+  <si>
+    <t>Forecasting API integration</t>
+  </si>
+  <si>
+    <t>Forecast analytics dashboard development</t>
+  </si>
+  <si>
+    <t>Forecast visualization charts</t>
+  </si>
+  <si>
+    <t>Farmer–Vendor communication module</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Conducted research on machine learning–based forecasting techniques and evaluated the limitations of the baseline Moving Average approach. Identified </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML.NET SSA (Singular Spectrum Analysis) Time Series Forecasting as a suitable ML-based approach for predicting vendor demand quantities using historical demand request data.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLDemandForecastingEngine.cs module using the ML.NET TimeSeries API. Developed the MLContext pipeline and configured SSA forecasting parameters including training window size, horizon prediction, and historical demand sequence preparation. Integrated the forecasting engine with DemandForecastService.cs to support ML-based demand predictions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tested the ML.NET forecasting pipeline using historical demand request data stored in the database. Verified training data extraction, demand sequence generation, and forecast output structure. Added model identification logic (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ModelName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) to support comparison between MovingAverage and MLNET_SSA forecast results.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Developed backend API endpoints in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DemandForecastController.cs to support generation and retrieval of ML forecasting results. Integrated forecast generation logic with database persistence through EF Core and ensured compatibility with existing forecasting workflows.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented frontend analytics pages </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VendorForecast.jsx and FarmerForecast.jsx to allow users to generate and view forecasting results. Connected frontend components with backend forecasting APIs using secure token-based authentication.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Developed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ForecastLineChart.jsx to visualize demand history and forecast predictions. Implemented chart-based representation of historical demand versus forecast results and integrated the chart component into both vendor and farmer analytics dashboards.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Designed and implemented a chat system allowing real-time communication between farmers and vendors. Developed backend components including </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ChatController.cs, ChatService.cs, ChatHub.cs, and database models Conversation.cs and ChatMessage.cs. Implemented frontend chat interfaces FarmerChat.jsx, VendorChat.jsx, and reusable component ChatBox.jsx, enabling users to exchange messages directly within the FarmVendor platform.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1703,6 +1837,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1736,7 +1877,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1971,24 +2112,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE6E6E6"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFE6E6E6"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFE6E6E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2244,10 +2372,13 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4525,27 +4656,103 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
-  <dimension ref="B1:D2"/>
+  <dimension ref="B2:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="82" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:4" ht="17.25" thickBot="1">
-      <c r="B2" s="89" t="s">
+    <row r="2" spans="2:4" ht="16.5">
+      <c r="B2" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="90" t="s">
+      <c r="D2" s="91" t="s">
         <v>167</v>
       </c>
     </row>
+    <row r="3" spans="2:4" ht="60">
+      <c r="B3" s="89">
+        <v>46091</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="75">
+      <c r="B4" s="89">
+        <v>46092</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="60">
+      <c r="B5" s="89">
+        <v>46093</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="60">
+      <c r="B6" s="90">
+        <v>46094</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="45">
+      <c r="B7" s="90"/>
+      <c r="C7" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="45">
+      <c r="B8" s="90">
+        <v>46097</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="90">
+      <c r="B9" s="90"/>
+      <c r="C9" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B741FB-5592-4292-93B7-86CF5BD5141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73566D62-B25F-41D2-9967-A820518BBFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="227">
   <si>
     <t>Date</t>
   </si>
@@ -1638,6 +1638,9 @@
     <t>Completed Progress report 4 and uploaded to blackboard and checked in to github repository.</t>
   </si>
   <si>
+    <t>Developed worklog document in professional way</t>
+  </si>
+  <si>
     <t>Forecasting model research and improvement</t>
   </si>
   <si>
@@ -1770,6 +1773,9 @@
       </rPr>
       <t>ChatController.cs, ChatService.cs, ChatHub.cs, and database models Conversation.cs and ChatMessage.cs. Implemented frontend chat interfaces FarmerChat.jsx, VendorChat.jsx, and reusable component ChatBox.jsx, enabling users to exchange messages directly within the FarmVendor platform.</t>
     </r>
+  </si>
+  <si>
+    <t>Added required file names accordingly with work done</t>
   </si>
 </sst>
 </file>
@@ -2116,7 +2122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2380,6 +2386,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4656,7 +4665,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -4680,10 +4689,10 @@
         <v>46091</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="75">
@@ -4691,10 +4700,10 @@
         <v>46092</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="60">
@@ -4702,10 +4711,10 @@
         <v>46093</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="60">
@@ -4713,45 +4722,54 @@
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="75">
       <c r="B7" s="90"/>
       <c r="C7" s="42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="45" customHeight="1">
       <c r="B8" s="90">
         <v>46097</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>216</v>
+      <c r="C8" s="92" t="s">
+        <v>217</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="90">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="120">
       <c r="B9" s="90"/>
-      <c r="C9" s="42" t="s">
-        <v>217</v>
+      <c r="C9" s="92" t="s">
+        <v>218</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>224</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="90"/>
+      <c r="C10" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B8:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73566D62-B25F-41D2-9967-A820518BBFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D71440-5CD0-42A0-BF48-C0940B90A6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="0" windowWidth="19350" windowHeight="20985" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Sheet5" sheetId="7" r:id="rId4"/>
     <sheet name="report4" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
-    <sheet name="report4 value added" sheetId="9" r:id="rId7"/>
+    <sheet name="report5" sheetId="10" r:id="rId7"/>
+    <sheet name="report4 value added" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="234">
   <si>
     <t>Date</t>
   </si>
@@ -1777,12 +1778,185 @@
   <si>
     <t>Added required file names accordingly with work done</t>
   </si>
+  <si>
+    <t>re</t>
+  </si>
+  <si>
+    <t>Implemented and tested the farmer–vendor chat module in the FarmVendor system. Added chat conversation creation and message flow between farmer and vendor users.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixed login-related user identification issues by updating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Login.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to store </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in localStorage correctly.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Resolved chat database and foreign key issues by verifying valid farmer and vendor IDs from the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AspNetUsers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> table and testing conversation creation successfully.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixed SignalR/CORS connection issues by updating backend configuration in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Program.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and retesting real-time chat connection.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Improved chat usability by replacing manual user ID entry with searchable selection of existing farmers and vendors using name/email search. Updated </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ChatController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>chatApi.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FarmerChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VendorChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tested the full chat workflow from both farmer and vendor sides, including conversation opening, message display, and sending messages in a more user-friendly interface.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1841,13 +2015,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2122,7 +2289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2333,62 +2500,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2690,20 +2860,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="76">
+      <c r="A2" s="79">
         <v>46035</v>
       </c>
-      <c r="B2" s="78">
+      <c r="B2" s="81">
         <v>2</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="83" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
       <c r="A3" s="80"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="84"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -2770,20 +2940,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="76">
+      <c r="A12" s="79">
         <v>46039</v>
       </c>
-      <c r="B12" s="78">
+      <c r="B12" s="81">
         <v>2</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="83" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="80"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="83"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -2866,10 +3036,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="76">
+      <c r="A22" s="79">
         <v>46049</v>
       </c>
-      <c r="B22" s="78">
+      <c r="B22" s="81">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -2877,17 +3047,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="77"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="82"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="76">
+      <c r="A24" s="79">
         <v>46051</v>
       </c>
-      <c r="B24" s="78">
+      <c r="B24" s="81">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -2895,8 +3065,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="77"/>
-      <c r="B25" s="79"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="82"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -2913,10 +3083,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="76">
+      <c r="A27" s="79">
         <v>46057</v>
       </c>
-      <c r="B27" s="78">
+      <c r="B27" s="81">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -2924,8 +3094,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="77"/>
-      <c r="B28" s="79"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="82"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -2964,29 +3134,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="74"/>
-      <c r="B32" s="75"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="74"/>
-      <c r="B33" s="75"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="85"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="74"/>
-      <c r="B34" s="75"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="74"/>
-      <c r="B35" s="75"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3184,12 +3354,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3198,6 +3362,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4330,233 +4500,233 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="86">
+      <c r="B3" s="89">
         <v>46091</v>
       </c>
-      <c r="C3" s="87">
+      <c r="C3" s="91">
         <v>6</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="74" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="84" t="s">
+      <c r="B4" s="89"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="85" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="85" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="85" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="86"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="85" t="s">
+      <c r="B8" s="89"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="86"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="85" t="s">
+      <c r="B9" s="89"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="88">
+      <c r="B10" s="90">
         <v>46092</v>
       </c>
-      <c r="C10" s="87">
+      <c r="C10" s="91">
         <v>4</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="75" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="88"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="85" t="s">
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="88"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="85" t="s">
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="88"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="85" t="s">
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="88">
+      <c r="B14" s="90">
         <v>46093</v>
       </c>
-      <c r="C14" s="87">
+      <c r="C14" s="91">
         <v>6</v>
       </c>
-      <c r="D14" s="85" t="s">
+      <c r="D14" s="75" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="88"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="85" t="s">
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="88"/>
-      <c r="C16" s="87"/>
-      <c r="D16" s="85" t="s">
+      <c r="B16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="88">
+      <c r="B17" s="90">
         <v>46094</v>
       </c>
-      <c r="C17" s="87">
+      <c r="C17" s="91">
         <v>4</v>
       </c>
-      <c r="D17" s="85" t="s">
+      <c r="D17" s="75" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="88"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="85" t="s">
+      <c r="B18" s="90"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="88"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="85" t="s">
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="88"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="85" t="s">
+      <c r="B20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="88">
+      <c r="B21" s="90">
         <v>46097</v>
       </c>
-      <c r="C21" s="87">
+      <c r="C21" s="91">
         <v>5</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="75" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="88"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="85" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="88"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="85" t="s">
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="88"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="85" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="88"/>
-      <c r="C25" s="87"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="88"/>
-      <c r="C26" s="87"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="88"/>
-      <c r="C27" s="87"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="88"/>
-      <c r="C28" s="87"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="88"/>
-      <c r="C29" s="87"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="88"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="85" t="s">
+      <c r="B30" s="90"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="75" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C21:C30"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C3:C9"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B21:B30"/>
-    <mergeCell ref="C21:C30"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C3:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4664,6 +4834,84 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="49.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="B2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60">
+      <c r="B3" s="50">
+        <v>46099</v>
+      </c>
+      <c r="C3" s="93">
+        <v>4</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45">
+      <c r="B4" s="49"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="49" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60">
+      <c r="B5" s="49"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="49" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45">
+      <c r="B6" s="49"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="49" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="75">
+      <c r="B7" s="49"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="49" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="60">
+      <c r="B8" s="49"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="49" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
   <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4674,18 +4922,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="16.5">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="D2" s="77" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="60">
-      <c r="B3" s="89">
+    <row r="3" spans="2:4" ht="90">
+      <c r="B3" s="76">
         <v>46091</v>
       </c>
       <c r="C3" s="42" t="s">
@@ -4695,8 +4943,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="75">
-      <c r="B4" s="89">
+    <row r="4" spans="2:4" ht="105">
+      <c r="B4" s="76">
         <v>46092</v>
       </c>
       <c r="C4" s="42" t="s">
@@ -4706,8 +4954,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="60">
-      <c r="B5" s="89">
+    <row r="5" spans="2:4" ht="90">
+      <c r="B5" s="76">
         <v>46093</v>
       </c>
       <c r="C5" s="42" t="s">
@@ -4717,8 +4965,8 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="60">
-      <c r="B6" s="90">
+    <row r="6" spans="2:4" ht="90">
+      <c r="B6" s="92">
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
@@ -4729,7 +4977,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="90"/>
+      <c r="B7" s="92"/>
       <c r="C7" s="42" t="s">
         <v>216</v>
       </c>
@@ -4738,10 +4986,10 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="90">
+      <c r="B8" s="92">
         <v>46097</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="78" t="s">
         <v>217</v>
       </c>
       <c r="D8" s="42" t="s">
@@ -4749,8 +4997,8 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="90"/>
-      <c r="C9" s="92" t="s">
+      <c r="B9" s="92"/>
+      <c r="C9" s="78" t="s">
         <v>218</v>
       </c>
       <c r="D9" s="42" t="s">
@@ -4758,7 +5006,7 @@
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="90"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="16" t="s">
         <v>211</v>
       </c>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D71440-5CD0-42A0-BF48-C0940B90A6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1CA080-69EE-4312-97F4-AC33921CDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
     <sheet name="report5" sheetId="10" r:id="rId7"/>
     <sheet name="report4 value added" sheetId="9" r:id="rId8"/>
+    <sheet name="report5 value added" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="244">
   <si>
     <t>Date</t>
   </si>
@@ -1950,6 +1951,36 @@
   </si>
   <si>
     <t>Tested the full chat workflow from both farmer and vendor sides, including conversation opening, message display, and sending messages in a more user-friendly interface.</t>
+  </si>
+  <si>
+    <t>Chat module integration and enhancement</t>
+  </si>
+  <si>
+    <t>Independently designed and integrated a real-time farmer–vendor chat system using SignalR within the existing ASP.NET Core + React architecture. Ensured secure communication using JWT-based authentication and proper user identification.</t>
+  </si>
+  <si>
+    <t>Debugging and system stabilization</t>
+  </si>
+  <si>
+    <t>Identified and resolved complex issues related to foreign key constraints, incorrect userId handling, and SignalR CORS/connection errors through debugging and configuration fixes.</t>
+  </si>
+  <si>
+    <t>User experience improvement</t>
+  </si>
+  <si>
+    <t>Enhanced usability by replacing manual ID-based chat initiation with a searchable dropdown using display name and email, making the system more practical and user-friendly.</t>
+  </si>
+  <si>
+    <t>Full-stack integration</t>
+  </si>
+  <si>
+    <t>Successfully connected backend chat APIs, database persistence, and frontend UI components, ensuring end-to-end functionality including conversation creation, message flow, and real-time updates.</t>
+  </si>
+  <si>
+    <t>System design improvement</t>
+  </si>
+  <si>
+    <t>Extended the system architecture to support scalable communication between farmers and vendors, aligning with the project goal of improving coordination and interaction within the supply chain platform.</t>
   </si>
 </sst>
 </file>
@@ -2289,7 +2320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2556,6 +2587,9 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -4863,7 +4897,7 @@
       <c r="B3" s="50">
         <v>46099</v>
       </c>
-      <c r="C3" s="93">
+      <c r="C3" s="94">
         <v>4</v>
       </c>
       <c r="D3" s="49" t="s">
@@ -4872,35 +4906,35 @@
     </row>
     <row r="4" spans="1:4" ht="45">
       <c r="B4" s="49"/>
-      <c r="C4" s="93"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="49" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60">
       <c r="B5" s="49"/>
-      <c r="C5" s="93"/>
+      <c r="C5" s="94"/>
       <c r="D5" s="49" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45">
       <c r="B6" s="49"/>
-      <c r="C6" s="93"/>
+      <c r="C6" s="94"/>
       <c r="D6" s="49" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="75">
       <c r="B7" s="49"/>
-      <c r="C7" s="93"/>
+      <c r="C7" s="94"/>
       <c r="D7" s="49" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60">
       <c r="B8" s="49"/>
-      <c r="C8" s="93"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="49" t="s">
         <v>233</v>
       </c>
@@ -5022,4 +5056,77 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+    <col min="4" max="4" width="65.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="60">
+      <c r="B3" s="50">
+        <v>46099</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="45">
+      <c r="B4" s="50"/>
+      <c r="C4" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="45">
+      <c r="B5" s="50"/>
+      <c r="C5" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="45">
+      <c r="B6" s="50"/>
+      <c r="C6" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="60">
+      <c r="B7" s="50"/>
+      <c r="C7" s="49" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1CA080-69EE-4312-97F4-AC33921CDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE76305-30EC-4193-9E69-BCCE8E1EF036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="245">
   <si>
     <t>Date</t>
   </si>
@@ -1981,6 +1981,9 @@
   </si>
   <si>
     <t>Extended the system architecture to support scalable communication between farmers and vendors, aligning with the project goal of improving coordination and interaction within the supply chain platform.</t>
+  </si>
+  <si>
+    <t>Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection. Developed backend APIs for vendor and product lookup with search functionality. Updated forecasting UI to include vendor selection and improved validation handling.</t>
   </si>
 </sst>
 </file>
@@ -2546,35 +2549,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2582,17 +2594,8 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2894,20 +2897,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="79">
+      <c r="A2" s="83">
         <v>46035</v>
       </c>
-      <c r="B2" s="81">
+      <c r="B2" s="85">
         <v>2</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="88" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="84"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="89"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -2974,20 +2977,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="79">
+      <c r="A12" s="83">
         <v>46039</v>
       </c>
-      <c r="B12" s="81">
+      <c r="B12" s="85">
         <v>2</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="88" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="80"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="90"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -3070,10 +3073,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="79">
+      <c r="A22" s="83">
         <v>46049</v>
       </c>
-      <c r="B22" s="81">
+      <c r="B22" s="85">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -3081,17 +3084,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="82"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="86"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="79">
+      <c r="A24" s="83">
         <v>46051</v>
       </c>
-      <c r="B24" s="81">
+      <c r="B24" s="85">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -3099,8 +3102,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="88"/>
-      <c r="B25" s="82"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="86"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -3117,10 +3120,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="79">
+      <c r="A27" s="83">
         <v>46057</v>
       </c>
-      <c r="B27" s="81">
+      <c r="B27" s="85">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3128,8 +3131,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="88"/>
-      <c r="B28" s="82"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="86"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -3168,29 +3171,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="85"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="82"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="85"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="82"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="85"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="85"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="82"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3388,6 +3391,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3396,12 +3405,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4534,7 +4537,7 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="89">
+      <c r="B3" s="92">
         <v>46091</v>
       </c>
       <c r="C3" s="91">
@@ -4545,49 +4548,49 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="89"/>
+      <c r="B4" s="92"/>
       <c r="C4" s="91"/>
       <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="89"/>
+      <c r="B5" s="92"/>
       <c r="C5" s="91"/>
       <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="89"/>
+      <c r="B6" s="92"/>
       <c r="C6" s="91"/>
       <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="89"/>
+      <c r="B7" s="92"/>
       <c r="C7" s="91"/>
       <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="89"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="91"/>
       <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="89"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="91"/>
       <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="90">
+      <c r="B10" s="93">
         <v>46092</v>
       </c>
       <c r="C10" s="91">
@@ -4598,28 +4601,28 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="90"/>
+      <c r="B11" s="93"/>
       <c r="C11" s="91"/>
       <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="90"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="91"/>
       <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="90"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="91"/>
       <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="90">
+      <c r="B14" s="93">
         <v>46093</v>
       </c>
       <c r="C14" s="91">
@@ -4630,21 +4633,21 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="90"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="91"/>
       <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="90"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="91"/>
       <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="90">
+      <c r="B17" s="93">
         <v>46094</v>
       </c>
       <c r="C17" s="91">
@@ -4655,28 +4658,28 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="90"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="91"/>
       <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="90"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="91"/>
       <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="90"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="91"/>
       <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="90">
+      <c r="B21" s="93">
         <v>46097</v>
       </c>
       <c r="C21" s="91">
@@ -4687,63 +4690,63 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="90"/>
+      <c r="B22" s="93"/>
       <c r="C22" s="91"/>
       <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="90"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="91"/>
       <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="90"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="91"/>
       <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="90"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="91"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="90"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="91"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="90"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="91"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="90"/>
+      <c r="B28" s="93"/>
       <c r="C28" s="91"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="90"/>
+      <c r="B29" s="93"/>
       <c r="C29" s="91"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="90"/>
+      <c r="B30" s="93"/>
       <c r="C30" s="91"/>
       <c r="D30" s="75" t="s">
         <v>210</v>
@@ -4751,16 +4754,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B30"/>
     <mergeCell ref="C21:C30"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4869,7 +4872,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -4897,7 +4900,7 @@
       <c r="B3" s="50">
         <v>46099</v>
       </c>
-      <c r="C3" s="94">
+      <c r="C3" s="80">
         <v>4</v>
       </c>
       <c r="D3" s="49" t="s">
@@ -4906,37 +4909,45 @@
     </row>
     <row r="4" spans="1:4" ht="45">
       <c r="B4" s="49"/>
-      <c r="C4" s="94"/>
+      <c r="C4" s="80"/>
       <c r="D4" s="49" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60">
       <c r="B5" s="49"/>
-      <c r="C5" s="94"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="49" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45">
       <c r="B6" s="49"/>
-      <c r="C6" s="94"/>
+      <c r="C6" s="80"/>
       <c r="D6" s="49" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="75">
       <c r="B7" s="49"/>
-      <c r="C7" s="94"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="49" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60">
       <c r="B8" s="49"/>
-      <c r="C8" s="94"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="49" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="17">
+        <v>46100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -5000,7 +5011,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="90">
-      <c r="B6" s="92">
+      <c r="B6" s="94">
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
@@ -5011,7 +5022,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="92"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="42" t="s">
         <v>216</v>
       </c>
@@ -5020,7 +5031,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="92">
+      <c r="B8" s="94">
         <v>46097</v>
       </c>
       <c r="C8" s="78" t="s">
@@ -5031,7 +5042,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="92"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="78" t="s">
         <v>218</v>
       </c>
@@ -5040,7 +5051,7 @@
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="92"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="16" t="s">
         <v>211</v>
       </c>
@@ -5069,13 +5080,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="79" t="s">
         <v>167</v>
       </c>
     </row>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE76305-30EC-4193-9E69-BCCE8E1EF036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951125F9-39D2-4C83-8FE7-ABBF3197F171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="252">
   <si>
     <t>Date</t>
   </si>
@@ -1983,7 +1983,129 @@
     <t>Extended the system architecture to support scalable communication between farmers and vendors, aligning with the project goal of improving coordination and interaction within the supply chain platform.</t>
   </si>
   <si>
-    <t>Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection. Developed backend APIs for vendor and product lookup with search functionality. Updated forecasting UI to include vendor selection and improved validation handling.</t>
+    <r>
+      <t xml:space="preserve">Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FarmerForecast.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Developed backend APIs for vendor and product lookup with search functionality in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DemandForecastController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (endpoints: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/vendors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). Updated API integration in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>forecastApi.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to support dynamic search queries and data fetching. Improved validation handling and request payload structure in forecasting workflow to correctly include vendorId and prevent API errors.</t>
+    </r>
+  </si>
+  <si>
+    <t>Value added through UI/UX and system integration improvements</t>
+  </si>
+  <si>
+    <t>Improved overall system usability by eliminating manual ID entry and introducing intuitive search-based selection for vendors and products. Enabled scalable and user-friendly data selection using dynamic backend filtering, enhancing real-world applicability. Strengthened frontend–backend integration by aligning API contracts and validation logic, reducing runtime errors. Contributed to better data accuracy and user adoption by ensuring correct entity selection before forecasting operations.</t>
+  </si>
+  <si>
+    <t>updated navigation bar with separate common file (FarmerSidebar.jsx,VendorSidebar.jsx,App.jsx) and updated all related .jsx file with import functionality and sidebar element insertion</t>
+  </si>
+  <si>
+    <t>code complexity decresed by common navigationbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decreased react code complexity and incorrect manual path </t>
+  </si>
+  <si>
+    <t>correct grammar befor submission</t>
+  </si>
+  <si>
+    <t>correct before submission</t>
   </si>
 </sst>
 </file>
@@ -2323,7 +2445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2596,6 +2718,15 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4872,20 +5003,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="49.140625" customWidth="1"/>
+    <col min="4" max="4" width="63.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="B2" s="67" t="s">
         <v>0</v>
       </c>
@@ -4896,7 +5027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60">
+    <row r="3" spans="1:5" ht="60">
       <c r="B3" s="50">
         <v>46099</v>
       </c>
@@ -4907,47 +5038,58 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45">
+    <row r="4" spans="1:5" ht="45">
       <c r="B4" s="49"/>
       <c r="C4" s="80"/>
       <c r="D4" s="49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60">
+    <row r="5" spans="1:5" ht="60">
       <c r="B5" s="49"/>
       <c r="C5" s="80"/>
       <c r="D5" s="49" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45">
+    <row r="6" spans="1:5" ht="45">
       <c r="B6" s="49"/>
       <c r="C6" s="80"/>
       <c r="D6" s="49" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="75">
+    <row r="7" spans="1:5" ht="75">
       <c r="B7" s="49"/>
       <c r="C7" s="80"/>
       <c r="D7" s="49" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60">
+    <row r="8" spans="1:5" ht="60">
       <c r="B8" s="49"/>
       <c r="C8" s="80"/>
       <c r="D8" s="49" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5" ht="135">
       <c r="B9" s="17">
         <v>46100</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="49" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="60">
+      <c r="D10" s="97" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5071,7 +5213,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -5079,7 +5221,7 @@
     <col min="4" max="4" width="65.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:5">
       <c r="B2" s="79" t="s">
         <v>0</v>
       </c>
@@ -5090,8 +5232,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="60">
-      <c r="B3" s="50">
+    <row r="3" spans="2:5" ht="60">
+      <c r="B3" s="96">
         <v>46099</v>
       </c>
       <c r="C3" s="49" t="s">
@@ -5101,7 +5243,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="45">
+    <row r="4" spans="2:5" ht="45">
       <c r="B4" s="50"/>
       <c r="C4" s="49" t="s">
         <v>236</v>
@@ -5110,7 +5252,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="45">
+    <row r="5" spans="2:5" ht="45">
       <c r="B5" s="50"/>
       <c r="C5" s="49" t="s">
         <v>238</v>
@@ -5119,7 +5261,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="45">
+    <row r="6" spans="2:5" ht="45">
       <c r="B6" s="50"/>
       <c r="C6" s="49" t="s">
         <v>240</v>
@@ -5128,7 +5270,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="60">
+    <row r="7" spans="2:5" ht="60">
       <c r="B7" s="50"/>
       <c r="C7" s="49" t="s">
         <v>242</v>
@@ -5137,7 +5279,30 @@
         <v>243</v>
       </c>
     </row>
+    <row r="8" spans="2:5" ht="120">
+      <c r="B8" s="95">
+        <v>46100</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="30">
+      <c r="C9" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="97" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951125F9-39D2-4C83-8FE7-ABBF3197F171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7BB8AD-4FF4-41B6-8727-D0D12739BE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="253">
   <si>
     <t>Date</t>
   </si>
@@ -2106,6 +2106,9 @@
   </si>
   <si>
     <t>correct before submission</t>
+  </si>
+  <si>
+    <t>to do : chack ml forecast for vendor and farmer and charts</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2726,6 +2729,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5003,7 +5009,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -5090,6 +5096,11 @@
       </c>
       <c r="E10" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" s="98" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7BB8AD-4FF4-41B6-8727-D0D12739BE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C211A9-A5DD-46C6-A500-CB418BA4603E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="259">
   <si>
     <t>Date</t>
   </si>
@@ -2109,6 +2109,181 @@
   </si>
   <si>
     <t>to do : chack ml forecast for vendor and farmer and charts</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Designed and implemented a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data-driven vendor recommendation system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using forecasting outputs and historical demand patterns.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Combined </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ML.NET forecasting results with business logic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to rank vendors based on demand, availability, and fulfillment potential.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enabled </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>decision support for farmers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by suggesting optimal vendors for dispatch planning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extended system from a transactional platform into an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intelligent recommendation-driven system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vendor recommendation module implementation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented ML-based vendor recommendation feature to identify top vendors for dispatching based on forecast demand, inventory availability, and historical request data. Developed backend logic in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FarmerRecommendationService.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and exposed API via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FarmerController.cs (/recommended-vendors)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Integrated frontend in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FarmerDashboard.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to display top recommended vendors dynamically.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2680,59 +2855,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3034,20 +3209,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="83">
+      <c r="A2" s="85">
         <v>46035</v>
       </c>
-      <c r="B2" s="85">
+      <c r="B2" s="87">
         <v>2</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="89" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="89"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="90"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -3114,20 +3289,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="83">
+      <c r="A12" s="85">
         <v>46039</v>
       </c>
-      <c r="B12" s="85">
+      <c r="B12" s="87">
         <v>2</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="89" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="87"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="90"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -3210,10 +3385,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="83">
+      <c r="A22" s="85">
         <v>46049</v>
       </c>
-      <c r="B22" s="85">
+      <c r="B22" s="87">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -3221,17 +3396,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="84"/>
-      <c r="B23" s="86"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="88"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="83">
+      <c r="A24" s="85">
         <v>46051</v>
       </c>
-      <c r="B24" s="85">
+      <c r="B24" s="87">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -3239,8 +3414,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="84"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -3257,10 +3432,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="83">
+      <c r="A27" s="85">
         <v>46057</v>
       </c>
-      <c r="B27" s="85">
+      <c r="B27" s="87">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3268,8 +3443,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="84"/>
-      <c r="B28" s="86"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="88"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -3308,29 +3483,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="81"/>
-      <c r="B32" s="82"/>
+      <c r="A32" s="93"/>
+      <c r="B32" s="91"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="81"/>
-      <c r="B33" s="82"/>
+      <c r="A33" s="93"/>
+      <c r="B33" s="91"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="81"/>
-      <c r="B34" s="82"/>
+      <c r="A34" s="93"/>
+      <c r="B34" s="91"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="81"/>
-      <c r="B35" s="82"/>
+      <c r="A35" s="93"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3528,12 +3703,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3542,6 +3711,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4674,10 +4849,10 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="92">
+      <c r="B3" s="95">
         <v>46091</v>
       </c>
-      <c r="C3" s="91">
+      <c r="C3" s="97">
         <v>6</v>
       </c>
       <c r="D3" s="74" t="s">
@@ -4685,52 +4860,52 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="92"/>
-      <c r="C4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="92"/>
-      <c r="C5" s="91"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="92"/>
-      <c r="C6" s="91"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="92"/>
-      <c r="C7" s="91"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="92"/>
-      <c r="C8" s="91"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="92"/>
-      <c r="C9" s="91"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="97"/>
       <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="93">
+      <c r="B10" s="96">
         <v>46092</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="97">
         <v>4</v>
       </c>
       <c r="D10" s="75" t="s">
@@ -4738,31 +4913,31 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="93"/>
-      <c r="C11" s="91"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="93"/>
-      <c r="C12" s="91"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="93"/>
-      <c r="C13" s="91"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="97"/>
       <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="93">
+      <c r="B14" s="96">
         <v>46093</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="97">
         <v>6</v>
       </c>
       <c r="D14" s="75" t="s">
@@ -4770,24 +4945,24 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="93"/>
-      <c r="C15" s="91"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="97"/>
       <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="93"/>
-      <c r="C16" s="91"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="93">
+      <c r="B17" s="96">
         <v>46094</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="97">
         <v>4</v>
       </c>
       <c r="D17" s="75" t="s">
@@ -4795,31 +4970,31 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="93"/>
-      <c r="C18" s="91"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="93"/>
-      <c r="C19" s="91"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="93"/>
-      <c r="C20" s="91"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="93">
+      <c r="B21" s="96">
         <v>46097</v>
       </c>
-      <c r="C21" s="91">
+      <c r="C21" s="97">
         <v>5</v>
       </c>
       <c r="D21" s="75" t="s">
@@ -4827,80 +5002,80 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="93"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="97"/>
       <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="93"/>
-      <c r="C23" s="91"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="97"/>
       <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="93"/>
-      <c r="C24" s="91"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="93"/>
-      <c r="C25" s="91"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="97"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="93"/>
-      <c r="C26" s="91"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="97"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="93"/>
-      <c r="C27" s="91"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="97"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="93"/>
-      <c r="C28" s="91"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="97"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="93"/>
-      <c r="C29" s="91"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="97"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="93"/>
-      <c r="C30" s="91"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="97"/>
       <c r="D30" s="75" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C21:C30"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C3:C9"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B21:B30"/>
-    <mergeCell ref="C21:C30"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C3:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5009,7 +5184,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -5033,7 +5208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60">
+    <row r="3" spans="1:5" ht="45">
       <c r="B3" s="50">
         <v>46099</v>
       </c>
@@ -5044,35 +5219,35 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45">
+    <row r="4" spans="1:5" ht="30">
       <c r="B4" s="49"/>
       <c r="C4" s="80"/>
       <c r="D4" s="49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="60">
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="49"/>
       <c r="C5" s="80"/>
       <c r="D5" s="49" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="45">
+    <row r="6" spans="1:5" ht="30">
       <c r="B6" s="49"/>
       <c r="C6" s="80"/>
       <c r="D6" s="49" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="75">
+    <row r="7" spans="1:5" ht="60">
       <c r="B7" s="49"/>
       <c r="C7" s="80"/>
       <c r="D7" s="49" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="60">
+    <row r="8" spans="1:5" ht="45">
       <c r="B8" s="49"/>
       <c r="C8" s="80"/>
       <c r="D8" s="49" t="s">
@@ -5091,7 +5266,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="60">
-      <c r="D10" s="97" t="s">
+      <c r="D10" s="83" t="s">
         <v>247</v>
       </c>
       <c r="E10" t="s">
@@ -5099,9 +5274,40 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="84" t="s">
         <v>252</v>
       </c>
+    </row>
+    <row r="13" spans="1:5" ht="105">
+      <c r="B13" s="50">
+        <v>46101</v>
+      </c>
+      <c r="C13" s="19">
+        <v>3</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5164,7 +5370,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="90">
-      <c r="B6" s="94">
+      <c r="B6" s="98">
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
@@ -5175,7 +5381,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="94"/>
+      <c r="B7" s="98"/>
       <c r="C7" s="42" t="s">
         <v>216</v>
       </c>
@@ -5184,7 +5390,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="94">
+      <c r="B8" s="98">
         <v>46097</v>
       </c>
       <c r="C8" s="78" t="s">
@@ -5195,7 +5401,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="94"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="78" t="s">
         <v>218</v>
       </c>
@@ -5204,7 +5410,7 @@
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="94"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="16" t="s">
         <v>211</v>
       </c>
@@ -5224,7 +5430,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
-  <dimension ref="B2:E9"/>
+  <dimension ref="B2:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -5244,7 +5450,7 @@
       </c>
     </row>
     <row r="3" spans="2:5" ht="60">
-      <c r="B3" s="96">
+      <c r="B3" s="82">
         <v>46099</v>
       </c>
       <c r="C3" s="49" t="s">
@@ -5291,7 +5497,7 @@
       </c>
     </row>
     <row r="8" spans="2:5" ht="120">
-      <c r="B8" s="95">
+      <c r="B8" s="81">
         <v>46100</v>
       </c>
       <c r="C8" s="49" t="s">
@@ -5302,14 +5508,40 @@
       </c>
     </row>
     <row r="9" spans="2:5" ht="30">
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="97" t="s">
+      <c r="D9" s="83" t="s">
         <v>249</v>
       </c>
       <c r="E9" t="s">
         <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="17">
+        <v>46101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="D12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="D13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="D14" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C211A9-A5DD-46C6-A500-CB418BA4603E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C424AE-AE44-40CC-BBFC-1B619F40E7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="260">
   <si>
     <t>Date</t>
   </si>
@@ -2284,6 +2284,9 @@
       </rPr>
       <t xml:space="preserve"> to display top recommended vendors dynamically.</t>
     </r>
+  </si>
+  <si>
+    <t>check y vendors not populating</t>
   </si>
 </sst>
 </file>
@@ -5292,7 +5295,9 @@
     <row r="14" spans="1:5">
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
+      <c r="D14" s="84" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="49"/>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\1dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C424AE-AE44-40CC-BBFC-1B619F40E7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5497F1-E1E3-4A0C-BF89-8A422FDB00EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="258">
   <si>
     <t>Date</t>
   </si>
@@ -1983,50 +1983,29 @@
     <t>Extended the system architecture to support scalable communication between farmers and vendors, aligning with the project goal of improving coordination and interaction within the supply chain platform.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FarmerForecast.jsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Developed backend APIs for vendor and product lookup with search functionality in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DemandForecastController.cs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (endpoints: </t>
+    <t>Value added through UI/UX and system integration improvements</t>
+  </si>
+  <si>
+    <t>Improved overall system usability by eliminating manual ID entry and introducing intuitive search-based selection for vendors and products. Enabled scalable and user-friendly data selection using dynamic backend filtering, enhancing real-world applicability. Strengthened frontend–backend integration by aligning API contracts and validation logic, reducing runtime errors. Contributed to better data accuracy and user adoption by ensuring correct entity selection before forecasting operations.</t>
+  </si>
+  <si>
+    <t>code complexity decresed by common navigationbar</t>
+  </si>
+  <si>
+    <t>correct before submission</t>
+  </si>
+  <si>
+    <t>to do : chack ml forecast for vendor and farmer and charts</t>
+  </si>
+  <si>
+    <t>Vendor recommendation module implementation</t>
+  </si>
+  <si>
+    <t>Implemented ML-based vendor recommendation feature to identify top vendors for dispatching based on forecast demand, inventory availability, and historical request data. Developed backend logic in FarmerRecommendationService.cs and exposed API via FarmerController.cs (/recommended-vendors). Integrated frontend in FarmerDashboard.jsx to display top recommended vendors dynamically.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection in FarmerForecast.jsx. Developed backend APIs for vendor and product lookup with search functionality in DemandForecastController.cs (endpoints: </t>
     </r>
     <r>
       <rPr>
@@ -2062,238 +2041,53 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">). Updated API integration in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>forecastApi.js</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to support dynamic search queries and data fetching. Improved validation handling and request payload structure in forecasting workflow to correctly include vendorId and prevent API errors.</t>
-    </r>
-  </si>
-  <si>
-    <t>Value added through UI/UX and system integration improvements</t>
-  </si>
-  <si>
-    <t>Improved overall system usability by eliminating manual ID entry and introducing intuitive search-based selection for vendors and products. Enabled scalable and user-friendly data selection using dynamic backend filtering, enhancing real-world applicability. Strengthened frontend–backend integration by aligning API contracts and validation logic, reducing runtime errors. Contributed to better data accuracy and user adoption by ensuring correct entity selection before forecasting operations.</t>
-  </si>
-  <si>
-    <t>updated navigation bar with separate common file (FarmerSidebar.jsx,VendorSidebar.jsx,App.jsx) and updated all related .jsx file with import functionality and sidebar element insertion</t>
-  </si>
-  <si>
-    <t>code complexity decresed by common navigationbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decreased react code complexity and incorrect manual path </t>
-  </si>
-  <si>
-    <t>correct grammar befor submission</t>
-  </si>
-  <si>
-    <t>correct before submission</t>
-  </si>
-  <si>
-    <t>to do : chack ml forecast for vendor and farmer and charts</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Designed and implemented a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>data-driven vendor recommendation system</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> using forecasting outputs and historical demand patterns.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Combined </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ML.NET forecasting results with business logic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to rank vendors based on demand, availability, and fulfillment potential.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Enabled </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>decision support for farmers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by suggesting optimal vendors for dispatch planning.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Extended system from a transactional platform into an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>intelligent recommendation-driven system</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Vendor recommendation module implementation</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implemented ML-based vendor recommendation feature to identify top vendors for dispatching based on forecast demand, inventory availability, and historical request data. Developed backend logic in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FarmerRecommendationService.cs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and exposed API via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FarmerController.cs (/recommended-vendors)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Integrated frontend in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FarmerDashboard.jsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to display top recommended vendors dynamically.</t>
-    </r>
-  </si>
-  <si>
-    <t>check y vendors not populating</t>
+      <t>). Updated API integration in forecastApi.js to support dynamic search queries and data fetching. Improved validation handling and request payload structure in forecasting workflow to correctly include vendorId and prevent API errors.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated the navigation bar by creating a separate common component file. Refactored FarmerSidebar.jsx, VendorSidebar.jsx, and App.jsx to import the shared component. All related </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> files were updated to include the new import structure and integrate the sidebar elements.</t>
+    </r>
+  </si>
+  <si>
+    <t>Reduced React code complexity by implementing a common navigation bar and eliminated incorrect manual routing paths.</t>
+  </si>
+  <si>
+    <t>Designed and implemented a data-driven vendor recommendation system using forecasting outputs and historical demand patterns.</t>
+  </si>
+  <si>
+    <t>Combined ML.NET forecasting results with business logic to rank vendors based on demand, availability, and fulfillment potential.</t>
+  </si>
+  <si>
+    <t>Enabled decision support for farmers by suggesting optimal vendors for dispatch planning.</t>
+  </si>
+  <si>
+    <t>Extended system from a transactional platform into an intelligent recommendation-driven system.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2359,6 +2153,13 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2626,7 +2427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2852,53 +2653,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2906,11 +2695,38 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3212,20 +3028,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="85">
+      <c r="A2" s="82">
         <v>46035</v>
       </c>
-      <c r="B2" s="87">
+      <c r="B2" s="84">
         <v>2</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="87" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
       <c r="A3" s="86"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="90"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="88"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -3292,20 +3108,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="85">
+      <c r="A12" s="82">
         <v>46039</v>
       </c>
-      <c r="B12" s="87">
+      <c r="B12" s="84">
         <v>2</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C12" s="87" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="86"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="89"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -3388,10 +3204,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="85">
+      <c r="A22" s="82">
         <v>46049</v>
       </c>
-      <c r="B22" s="87">
+      <c r="B22" s="84">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -3399,17 +3215,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="88"/>
+      <c r="A23" s="83"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="85">
+      <c r="A24" s="82">
         <v>46051</v>
       </c>
-      <c r="B24" s="87">
+      <c r="B24" s="84">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -3417,8 +3233,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="94"/>
-      <c r="B25" s="88"/>
+      <c r="A25" s="83"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -3435,10 +3251,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="85">
+      <c r="A27" s="82">
         <v>46057</v>
       </c>
-      <c r="B27" s="87">
+      <c r="B27" s="84">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3446,8 +3262,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="88"/>
+      <c r="A28" s="83"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -3486,29 +3302,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="93"/>
-      <c r="B32" s="91"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="81"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="93"/>
-      <c r="B33" s="91"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="81"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="93"/>
-      <c r="B34" s="91"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="81"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="93"/>
-      <c r="B35" s="91"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="81"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3706,6 +3522,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3714,12 +3536,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4852,10 +4668,10 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="95">
+      <c r="B3" s="91">
         <v>46091</v>
       </c>
-      <c r="C3" s="97">
+      <c r="C3" s="90">
         <v>6</v>
       </c>
       <c r="D3" s="74" t="s">
@@ -4863,52 +4679,52 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="95"/>
-      <c r="C4" s="97"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="90"/>
       <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="95"/>
-      <c r="C5" s="97"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="90"/>
       <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="95"/>
-      <c r="C6" s="97"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="90"/>
       <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="95"/>
-      <c r="C7" s="97"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="90"/>
       <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="95"/>
-      <c r="C8" s="97"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="90"/>
       <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="95"/>
-      <c r="C9" s="97"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="90"/>
       <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="96">
+      <c r="B10" s="92">
         <v>46092</v>
       </c>
-      <c r="C10" s="97">
+      <c r="C10" s="90">
         <v>4</v>
       </c>
       <c r="D10" s="75" t="s">
@@ -4916,31 +4732,31 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="96"/>
-      <c r="C11" s="97"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="90"/>
       <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="96"/>
-      <c r="C12" s="97"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="90"/>
       <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="96"/>
-      <c r="C13" s="97"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="90"/>
       <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="96">
+      <c r="B14" s="92">
         <v>46093</v>
       </c>
-      <c r="C14" s="97">
+      <c r="C14" s="90">
         <v>6</v>
       </c>
       <c r="D14" s="75" t="s">
@@ -4948,24 +4764,24 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="96"/>
-      <c r="C15" s="97"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="96"/>
-      <c r="C16" s="97"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="90"/>
       <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="96">
+      <c r="B17" s="92">
         <v>46094</v>
       </c>
-      <c r="C17" s="97">
+      <c r="C17" s="90">
         <v>4</v>
       </c>
       <c r="D17" s="75" t="s">
@@ -4973,31 +4789,31 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="96"/>
-      <c r="C18" s="97"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="90"/>
       <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="96"/>
-      <c r="C19" s="97"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="90"/>
       <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="96"/>
-      <c r="C20" s="97"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="90"/>
       <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="96">
+      <c r="B21" s="92">
         <v>46097</v>
       </c>
-      <c r="C21" s="97">
+      <c r="C21" s="90">
         <v>5</v>
       </c>
       <c r="D21" s="75" t="s">
@@ -5005,80 +4821,80 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="96"/>
-      <c r="C22" s="97"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="96"/>
-      <c r="C23" s="97"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="96"/>
-      <c r="C24" s="97"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="96"/>
-      <c r="C25" s="97"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="96"/>
-      <c r="C26" s="97"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="96"/>
-      <c r="C27" s="97"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="96"/>
-      <c r="C28" s="97"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="90"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="96"/>
-      <c r="C29" s="97"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="90"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="96"/>
-      <c r="C30" s="97"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="90"/>
       <c r="D30" s="75" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B30"/>
     <mergeCell ref="C21:C30"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5187,7 +5003,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -5212,109 +5028,107 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="45">
-      <c r="B3" s="50">
+      <c r="B3" s="94">
         <v>46099</v>
       </c>
-      <c r="C3" s="80">
+      <c r="C3" s="95">
         <v>4</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="41" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30">
-      <c r="B4" s="49"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="49" t="s">
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="41" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45">
-      <c r="B5" s="49"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30">
-      <c r="B6" s="49"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="49" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="60">
-      <c r="B7" s="49"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="49" t="s">
+      <c r="B7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="41" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45">
-      <c r="B8" s="49"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="49" t="s">
+      <c r="B8" s="94"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="41" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="135">
-      <c r="B9" s="17">
+      <c r="B9" s="92">
         <v>46100</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="90">
         <v>3</v>
       </c>
-      <c r="D9" s="49" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="60">
-      <c r="D10" s="83" t="s">
+      <c r="D9" s="42" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="75">
+      <c r="B10" s="92"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="96" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" t="s">
         <v>247</v>
       </c>
-      <c r="E10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="D12" s="84" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="105">
-      <c r="B13" s="50">
+    </row>
+    <row r="11" spans="1:5" ht="105">
+      <c r="B11" s="97">
         <v>46101</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C11" s="98">
         <v>3</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>258</v>
-      </c>
+      <c r="D11" s="99" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
-      <c r="D14" s="84" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
+      <c r="D14" s="49"/>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="79" t="s">
+        <v>248</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="C9:C10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -5375,7 +5189,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="90">
-      <c r="B6" s="98">
+      <c r="B6" s="93">
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
@@ -5386,7 +5200,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="98"/>
+      <c r="B7" s="93"/>
       <c r="C7" s="42" t="s">
         <v>216</v>
       </c>
@@ -5395,7 +5209,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="98">
+      <c r="B8" s="93">
         <v>46097</v>
       </c>
       <c r="C8" s="78" t="s">
@@ -5406,7 +5220,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="98"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="78" t="s">
         <v>218</v>
       </c>
@@ -5415,7 +5229,7 @@
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="98"/>
+      <c r="B10" s="93"/>
       <c r="C10" s="16" t="s">
         <v>211</v>
       </c>
@@ -5435,121 +5249,131 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
-  <dimension ref="B2:E14"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
     <col min="3" max="3" width="28.28515625" customWidth="1"/>
-    <col min="4" max="4" width="65.28515625" customWidth="1"/>
+    <col min="4" max="4" width="54.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
-      <c r="B2" s="79" t="s">
+    <row r="2" spans="2:4">
+      <c r="B2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="67" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="60">
-      <c r="B3" s="82">
+    <row r="3" spans="2:4" ht="60">
+      <c r="B3" s="94">
         <v>46099</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="26" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="45">
-      <c r="B4" s="50"/>
-      <c r="C4" s="49" t="s">
+    <row r="4" spans="2:4" ht="45">
+      <c r="B4" s="94"/>
+      <c r="C4" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="26" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="45">
-      <c r="B5" s="50"/>
-      <c r="C5" s="49" t="s">
+    <row r="5" spans="2:4" ht="45">
+      <c r="B5" s="94"/>
+      <c r="C5" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="26" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="45">
-      <c r="B6" s="50"/>
-      <c r="C6" s="49" t="s">
+    <row r="6" spans="2:4" ht="45">
+      <c r="B6" s="94"/>
+      <c r="C6" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="26" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="60">
-      <c r="B7" s="50"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" spans="2:4" ht="60">
+      <c r="B7" s="94"/>
+      <c r="C7" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="26" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="120">
-      <c r="B8" s="81">
+    <row r="8" spans="2:4" ht="120">
+      <c r="B8" s="92">
         <v>46100</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="49" t="s">
+    </row>
+    <row r="9" spans="2:4" ht="30">
+      <c r="B9" s="92"/>
+      <c r="C9" s="100" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" ht="30">
-      <c r="C9" s="83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="30">
+      <c r="B10" s="92">
+        <v>46101</v>
+      </c>
+      <c r="C10" s="101" t="s">
         <v>249</v>
       </c>
-      <c r="E9" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="17">
-        <v>46101</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D10" s="102" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="30">
+      <c r="B11" s="92"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="103" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="30">
+      <c r="B12" s="92"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="103" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="30">
+      <c r="B13" s="92"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="103" t="s">
         <v>257</v>
       </c>
-      <c r="D11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="D12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="D13" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="D14" t="s">
-        <v>256</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\1dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5497F1-E1E3-4A0C-BF89-8A422FDB00EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C89141F-1C65-48A9-B050-48D12530E8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="260">
   <si>
     <t>Date</t>
   </si>
@@ -2082,12 +2082,18 @@
   <si>
     <t>Extended system from a transactional platform into an intelligent recommendation-driven system.</t>
   </si>
+  <si>
+    <t>add frontend farmer vendor location</t>
+  </si>
+  <si>
+    <t>connect with aspnetuser table data</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2153,13 +2159,6 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2656,77 +2655,77 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3028,20 +3027,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="82">
+      <c r="A2" s="87">
         <v>46035</v>
       </c>
-      <c r="B2" s="84">
+      <c r="B2" s="89">
         <v>2</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="91" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="86"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="88"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="92"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -3108,20 +3107,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="82">
+      <c r="A12" s="87">
         <v>46039</v>
       </c>
-      <c r="B12" s="84">
+      <c r="B12" s="89">
         <v>2</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="91" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="89"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="94"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -3204,10 +3203,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="82">
+      <c r="A22" s="87">
         <v>46049</v>
       </c>
-      <c r="B22" s="84">
+      <c r="B22" s="89">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -3215,17 +3214,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="83"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="96"/>
+      <c r="B23" s="90"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="82">
+      <c r="A24" s="87">
         <v>46051</v>
       </c>
-      <c r="B24" s="84">
+      <c r="B24" s="89">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -3233,8 +3232,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="83"/>
-      <c r="B25" s="85"/>
+      <c r="A25" s="96"/>
+      <c r="B25" s="90"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -3251,10 +3250,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="82">
+      <c r="A27" s="87">
         <v>46057</v>
       </c>
-      <c r="B27" s="84">
+      <c r="B27" s="89">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3262,8 +3261,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="83"/>
-      <c r="B28" s="85"/>
+      <c r="A28" s="96"/>
+      <c r="B28" s="90"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -3302,29 +3301,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="80"/>
-      <c r="B32" s="81"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="80"/>
-      <c r="B33" s="81"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="93"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="80"/>
-      <c r="B34" s="81"/>
+      <c r="A34" s="95"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="80"/>
-      <c r="B35" s="81"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3522,12 +3521,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3536,6 +3529,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4668,10 +4667,10 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="91">
+      <c r="B3" s="97">
         <v>46091</v>
       </c>
-      <c r="C3" s="90">
+      <c r="C3" s="99">
         <v>6</v>
       </c>
       <c r="D3" s="74" t="s">
@@ -4679,52 +4678,52 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="91"/>
-      <c r="C4" s="90"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="91"/>
-      <c r="C5" s="90"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="91"/>
-      <c r="C6" s="90"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="99"/>
       <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="91"/>
-      <c r="C7" s="90"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="91"/>
-      <c r="C8" s="90"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="91"/>
-      <c r="C9" s="90"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="92">
+      <c r="B10" s="98">
         <v>46092</v>
       </c>
-      <c r="C10" s="90">
+      <c r="C10" s="99">
         <v>4</v>
       </c>
       <c r="D10" s="75" t="s">
@@ -4732,31 +4731,31 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="92"/>
-      <c r="C11" s="90"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="99"/>
       <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="92"/>
-      <c r="C12" s="90"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
       <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="92"/>
-      <c r="C13" s="90"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="99"/>
       <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="92">
+      <c r="B14" s="98">
         <v>46093</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="99">
         <v>6</v>
       </c>
       <c r="D14" s="75" t="s">
@@ -4764,24 +4763,24 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="92"/>
-      <c r="C15" s="90"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="92"/>
-      <c r="C16" s="90"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="92">
+      <c r="B17" s="98">
         <v>46094</v>
       </c>
-      <c r="C17" s="90">
+      <c r="C17" s="99">
         <v>4</v>
       </c>
       <c r="D17" s="75" t="s">
@@ -4789,31 +4788,31 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="92"/>
-      <c r="C18" s="90"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="92"/>
-      <c r="C19" s="90"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="92"/>
-      <c r="C20" s="90"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="92">
+      <c r="B21" s="98">
         <v>46097</v>
       </c>
-      <c r="C21" s="90">
+      <c r="C21" s="99">
         <v>5</v>
       </c>
       <c r="D21" s="75" t="s">
@@ -4821,80 +4820,80 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="92"/>
-      <c r="C22" s="90"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="92"/>
-      <c r="C23" s="90"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="92"/>
-      <c r="C24" s="90"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="92"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="99"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="92"/>
-      <c r="C26" s="90"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="92"/>
-      <c r="C27" s="90"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="92"/>
-      <c r="C28" s="90"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="92"/>
-      <c r="C29" s="90"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="92"/>
-      <c r="C30" s="90"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
       <c r="D30" s="75" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C21:C30"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C3:C9"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B21:B30"/>
-    <mergeCell ref="C21:C30"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C3:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5003,7 +5002,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -5028,10 +5027,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="45">
-      <c r="B3" s="94">
+      <c r="B3" s="100">
         <v>46099</v>
       </c>
-      <c r="C3" s="95">
+      <c r="C3" s="101">
         <v>4</v>
       </c>
       <c r="D3" s="41" t="s">
@@ -5039,45 +5038,45 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="30">
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="101"/>
       <c r="D4" s="41" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45">
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30">
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="60">
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="41" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45">
-      <c r="B8" s="94"/>
-      <c r="C8" s="95"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="41" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="135">
-      <c r="B9" s="92">
+      <c r="B9" s="98">
         <v>46100</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="99">
         <v>3</v>
       </c>
       <c r="D9" s="42" t="s">
@@ -5085,9 +5084,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="75">
-      <c r="B10" s="92"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="96" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="80" t="s">
         <v>252</v>
       </c>
       <c r="E10" t="s">
@@ -5095,13 +5094,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="105">
-      <c r="B11" s="97">
+      <c r="B11" s="81">
         <v>46101</v>
       </c>
-      <c r="C11" s="98">
+      <c r="C11" s="82">
         <v>3</v>
       </c>
-      <c r="D11" s="99" t="s">
+      <c r="D11" s="83" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5120,6 +5119,16 @@
       <c r="C22" s="49"/>
       <c r="D22" s="79" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="D24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="D25" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5189,7 +5198,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="90">
-      <c r="B6" s="93">
+      <c r="B6" s="102">
         <v>46094</v>
       </c>
       <c r="C6" s="42" t="s">
@@ -5200,7 +5209,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="93"/>
+      <c r="B7" s="102"/>
       <c r="C7" s="42" t="s">
         <v>216</v>
       </c>
@@ -5209,7 +5218,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="93">
+      <c r="B8" s="102">
         <v>46097</v>
       </c>
       <c r="C8" s="78" t="s">
@@ -5220,7 +5229,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="93"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="78" t="s">
         <v>218</v>
       </c>
@@ -5229,7 +5238,7 @@
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="93"/>
+      <c r="B10" s="102"/>
       <c r="C10" s="16" t="s">
         <v>211</v>
       </c>
@@ -5268,8 +5277,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="60">
-      <c r="B3" s="94">
+    <row r="3" spans="2:4" ht="75">
+      <c r="B3" s="100">
         <v>46099</v>
       </c>
       <c r="C3" s="26" t="s">
@@ -5279,8 +5288,8 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="45">
-      <c r="B4" s="94"/>
+    <row r="4" spans="2:4" ht="60">
+      <c r="B4" s="100"/>
       <c r="C4" s="26" t="s">
         <v>236</v>
       </c>
@@ -5288,8 +5297,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="94"/>
+    <row r="5" spans="2:4" ht="60">
+      <c r="B5" s="100"/>
       <c r="C5" s="26" t="s">
         <v>238</v>
       </c>
@@ -5297,8 +5306,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="94"/>
+    <row r="6" spans="2:4" ht="60">
+      <c r="B6" s="100"/>
       <c r="C6" s="26" t="s">
         <v>240</v>
       </c>
@@ -5307,7 +5316,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="94"/>
+      <c r="B7" s="100"/>
       <c r="C7" s="26" t="s">
         <v>242</v>
       </c>
@@ -5315,8 +5324,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="120">
-      <c r="B8" s="92">
+    <row r="8" spans="2:4" ht="135">
+      <c r="B8" s="98">
         <v>46100</v>
       </c>
       <c r="C8" s="26" t="s">
@@ -5326,44 +5335,44 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="30">
-      <c r="B9" s="92"/>
-      <c r="C9" s="100" t="s">
+    <row r="9" spans="2:4" ht="45">
+      <c r="B9" s="98"/>
+      <c r="C9" s="84" t="s">
         <v>246</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="92">
+    <row r="10" spans="2:4" ht="45">
+      <c r="B10" s="98">
         <v>46101</v>
       </c>
-      <c r="C10" s="101" t="s">
+      <c r="C10" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="85" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="92"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="103" t="s">
+    <row r="11" spans="2:4" ht="45">
+      <c r="B11" s="98"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="86" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="30">
-      <c r="B12" s="92"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="103" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="86" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="30">
-      <c r="B13" s="92"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="103" t="s">
+      <c r="B13" s="98"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="86" t="s">
         <v>257</v>
       </c>
     </row>

--- a/ReportsAndDocuments/worklog.xlsx
+++ b/ReportsAndDocuments/worklog.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C89141F-1C65-48A9-B050-48D12530E8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28FAFA-7D52-47C2-AE11-1D269576CA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1 (2)" sheetId="8" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId4"/>
-    <sheet name="report4" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
-    <sheet name="report5" sheetId="10" r:id="rId7"/>
-    <sheet name="report4 value added" sheetId="9" r:id="rId8"/>
-    <sheet name="report5 value added" sheetId="11" r:id="rId9"/>
+    <sheet name="report1" sheetId="12" r:id="rId4"/>
+    <sheet name="final" sheetId="13" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId6"/>
+    <sheet name="report4" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId8"/>
+    <sheet name="report5" sheetId="10" r:id="rId9"/>
+    <sheet name="report4 value added" sheetId="9" r:id="rId10"/>
+    <sheet name="report5 value added" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="372">
   <si>
     <t>Date</t>
   </si>
@@ -2088,12 +2090,842 @@
   <si>
     <t>connect with aspnetuser table data</t>
   </si>
+  <si>
+    <t>No. of Hours</t>
+  </si>
+  <si>
+    <t>Description of Work Done</t>
+  </si>
+  <si>
+    <t>Finalized the research idea for the FarmVendor application by clearly defining the problem statement and project scope.</t>
+  </si>
+  <si>
+    <t>Installed basic development tools including .NET SDK, Visual Studio Code, and SQL Server LocalDB.</t>
+  </si>
+  <si>
+    <t>Created a local database and initial React web application. Tested application execution in the browser and resolved multiple dependency installation issues.</t>
+  </si>
+  <si>
+    <t>Integrated ASP.NET Core Web API (.NET 8.0). Configured SQL Server LocalDB (FarmVendorDb), implemented ASP.NET Identity, defined Farmer and Vendor roles, and set up JWT authentication.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tested authentication endpoints using Postman, including </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>POST /api/auth/register</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>POST /api/auth/login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Attended project idea re‑evaluation meeting with instructor (Madam Priya) and refined the research direction.</t>
+  </si>
+  <si>
+    <t>Conducted initial research on existing mobile and web‑based agricultural supply‑chain applications.</t>
+  </si>
+  <si>
+    <t>Performed background research and literature review related to demand forecasting and supply‑chain systems.</t>
+  </si>
+  <si>
+    <t>Conducted research on React integration with ASP.NET backend architecture.</t>
+  </si>
+  <si>
+    <t>Continued research proposal development, focusing on feature scope and system design.</t>
+  </si>
+  <si>
+    <t>Finalized the research proposal and prepared it for submission.</t>
+  </si>
+  <si>
+    <t>Reviewed submitted proposal feedback with instructor and made modifications to the data‑collection and forecasting strategy.</t>
+  </si>
+  <si>
+    <t>Implemented JWT authorization configuration and secured API endpoints with role‑based access control.</t>
+  </si>
+  <si>
+    <t>Moved GitHub repository to the root directory and cleaned unused project artifacts.</t>
+  </si>
+  <si>
+    <t>Created initial frontend sketches for the Farmer Dashboard and planned React component structure. Downloaded and configured required React dependencies.</t>
+  </si>
+  <si>
+    <t>Resolved installation and configuration issues related to Node.js and npm.</t>
+  </si>
+  <si>
+    <t>Completed login and registration UI design. Added dashboard CSS styling and modified application routing for Farmer and Vendor dashboards.</t>
+  </si>
+  <si>
+    <t>Uploaded modified proposal to GitHub. Updated progress report 1, linked working code screenshots, and verified GitHub repository structure.</t>
+  </si>
+  <si>
+    <t> 5</t>
+  </si>
+  <si>
+    <t> 3</t>
+  </si>
+  <si>
+    <t> 6</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VendorDashboard.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and integrated modal-based demand request creation with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VendorDemandRequestsController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Created the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DemandForecast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> model, supporting DTOs, and required database updates for forecast storage.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DispatchOptimizationService.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> using greedy baseline allocation logic based on forecast demand and available farmer inventory.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added automatic score updates for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Delivered</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cancelled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> dispatch events.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added and updated files required for relationship scoring, including </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RelationshipStat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RelationshipScoreRowDto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RelationshipScoreService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RelationshipStatsController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrated score update logic into </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VendorDispatchesController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> confirm delivery flow and outlined remaining frontend analytics views for forecast, optimization, and relationship endpoints.</t>
+    </r>
+  </si>
+  <si>
+    <t>Developed Progress report3</t>
+  </si>
+  <si>
+    <t>Individual checking</t>
+  </si>
+  <si>
+    <t>changing research baseline model to ML related model which focus on ML.NET’s forecasting task</t>
+  </si>
+  <si>
+    <t>Researched machine learning–based forecasting approaches and identified ML.NET SSA (Singular Spectrum Analysis) time series forecasting as a more suitable ML-driven model for demand prediction.</t>
+  </si>
+  <si>
+    <t>Updated research direction by replacing the baseline-only approach with an ML-focused forecasting implementation using ML.NET TimeSeries API and refactored the forecasting workflow in DemandForecastService.cs</t>
+  </si>
+  <si>
+    <t>Studied ML.NET forecasting pipeline structure including SSA training window, horizon prediction, model retraining, and demand sequence preparation from historical demand request data, preparing the implementation structure for MLDemandForecastEngine.cs</t>
+  </si>
+  <si>
+    <t>Studied ML.NET forecasting pipeline structure including SSA training window, horizon prediction, model retraining, and demand sequence preparation from historical demand request data.</t>
+  </si>
+  <si>
+    <t>Refactored forecasting architecture to support multiple forecasting models (Moving Average + ML.NET SSA) and updated related models including DemandForecast.cs, GenerateForecastDto.cs, and DemandForecastRowDto.cs</t>
+  </si>
+  <si>
+    <t>Implemented the ML.NET forecasting engine inside the backend service layer.</t>
+  </si>
+  <si>
+    <t>Created MLDemandForecastEngine.cs to train ML.NET models using historical demand request quantities stored in the database.</t>
+  </si>
+  <si>
+    <t>Implemented time-series training pipeline using MLContext and SSA forecasting trainer to predict future vendor demand quantities inside MLDemandForecastEngine.cs</t>
+  </si>
+  <si>
+    <t>Integrated ML forecast generation into the existing forecasting workflow by updating DemandForecastService.cs so prediction results can be stored in the DemandForecast table</t>
+  </si>
+  <si>
+    <t>Verified training data extraction, forecast horizon configuration, and prediction output structure in MLDemandForecastEngine.cs</t>
+  </si>
+  <si>
+    <t>Added model identification field (ModelName) to distinguish forecast outputs from MovingAverage vs MLNET_SSA models and updated related structures in DemandForecast.cs and DemandForecastRowDto.cs</t>
+  </si>
+  <si>
+    <t>Implemented API logic in ForecastController.cs for generating ML forecasts and storing prediction results in the database.</t>
+  </si>
+  <si>
+    <t>Ensured compatibility between backend forecasting APIs and frontend analytics components by updating request/response DTOs such as GenerateForecastDto.cs and DemandForecastRowDto.cs</t>
+  </si>
+  <si>
+    <t>Implemented Vendor Forecast Analytics page in VendorForecast.jsx including forecast generation form and model comparison module between Moving Average and ML.NET models.</t>
+  </si>
+  <si>
+    <t>Integrated forecasting APIs with React frontend components using secure token-based authentication through forecastApi.js and existing route protection logic</t>
+  </si>
+  <si>
+    <t>Added forecast visualization charts to the analytics dashboard to represent demand history and forecast trends visually.</t>
+  </si>
+  <si>
+    <t>Implemented chart component ForecastLineChart.jsx to display historical demand data alongside forecast predictions.</t>
+  </si>
+  <si>
+    <t>Integrated chart component into both analytics pages VendorForecast.jsx and FarmerForecast.jsx to provide graphical interpretation of forecasting results.</t>
+  </si>
+  <si>
+    <t>Began implementation of a real-time communication feature between farmers and vendors within the FarmVendor system.</t>
+  </si>
+  <si>
+    <t>Designed the chat module architecture and developed frontend messaging components FarmerChat.jsx and VendorChat.jsx.</t>
+  </si>
+  <si>
+    <t>Updated authentication logic in Login.jsx to store userId in localStorage to support message sender identification for chat communication.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixed login-related user identification issues by updating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Login.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to store </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in localStorage correctly.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Resolved chat database and foreign key issues by verifying valid farmer and vendor IDs from the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AspNetUsers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> table and testing conversation creation successfully.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixed SignalR/CORS connection issues by updating backend configuration in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Program.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and retesting real-time chat connection.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Improved chat usability by replacing manual user ID entry with searchable selection of existing farmers and vendors using name/email search. Updated </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ChatController.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chatApi.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FarmerChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VendorChat.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enhanced user experience of forecasting interface by replacing manual userId inputs with searchable dropdowns for vendor and product selection in FarmerForecast.jsx. Developed backend APIs for vendor and product lookup with search functionality in DemandForecastController.cs (endpoints: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/vendors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>). Updated API integration in forecastApi.js to support dynamic search queries and data fetching. Improved validation handling and request payload structure in forecasting workflow to correctly include vendorId and prevent API errors.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Updated the navigation bar by creating a separate common component file. Refactored FarmerSidebar.jsx, VendorSidebar.jsx, and App.jsx to import the shared component. All related </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.jsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files were updated to include the new import structure and integrate the sidebar elements.</t>
+    </r>
+  </si>
+  <si>
+    <t>Populated the system with additional historical demand data to support forecasting experiments and verified that ML.NET SSA forecast rows were generated successfully in the DemandForecast table.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Debugged why recommended vendors and charts were not appearing by checking forecast dates, inventory overlap, API responses, and endpoint usage. Fixed forecasting chart integration by correcting the chart API endpoint in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>forecastApi.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, updating chart-loading logic to use the selected forecasting model, and refining </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DemandForecastService.cs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> chart data retrieval to return recent historical values together with matching forecast values from the selected date onward. Continued testing of farmer-specific recommended vendors and confirmed that recommendation results change based on the logged-in farmer’s inventory and forecast matching data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Progress report 5 submission</t>
+  </si>
+  <si>
+    <t>Enhanced forecasting dashboard UI with advanced settings panel including vendor, product, date, model, and horizon selection.</t>
+  </si>
+  <si>
+    <t>Implemented default parameter auto-loading for vendor, product, and forecast date to improve usability.</t>
+  </si>
+  <si>
+    <t>Improved error handling for forecast generation and API failures in FarmerForecast.jsx.</t>
+  </si>
+  <si>
+    <t>Implemented CSV export functionality for forecast results.</t>
+  </si>
+  <si>
+    <t>Added Export button to forecasting dashboard and generated downloadable CSV file including vendor name, product name, forecast date, quantity, model, and created date.</t>
+  </si>
+  <si>
+    <t>Ensured removal of internal IDs from export and replaced with user-friendly names.</t>
+  </si>
+  <si>
+    <t>Upgraded forecast visualization to support multi-vendor comparison charts.</t>
+  </si>
+  <si>
+    <t>Developed MultiVendorForecastLineChart.jsx to display up to 4 vendors in a single graph with distinct colors and legends.</t>
+  </si>
+  <si>
+    <t>Integrated vendor selection logic allowing dynamic selection of top vendors from forecast results.</t>
+  </si>
+  <si>
+    <t>Implemented backend API enhancement for chart data retrieval per vendor and product.</t>
+  </si>
+  <si>
+    <t>Added filtering logic in DemandForecastController.cs to support vendorId, productId, and forecastDate.</t>
+  </si>
+  <si>
+    <t>Improved chart API response to include both historical demand and forecast data series.</t>
+  </si>
+  <si>
+    <t>Enhanced frontend chart rendering logic by fixing dataset mapping and handling missing/null values.</t>
+  </si>
+  <si>
+    <t>Resolved chart data alignment issues between historical and forecast series.</t>
+  </si>
+  <si>
+    <t>Improved chart readability with legend labels and consistent formatting.</t>
+  </si>
+  <si>
+    <t>Implemented vendor filtering logic based on farmer inventory.</t>
+  </si>
+  <si>
+    <t>Restricted vendors to only those having demand requests matching farmer’s available products.</t>
+  </si>
+  <si>
+    <t>Updated backend logic in DemandForecastService.cs and FarmerController.cs to support real-world filtering conditions.</t>
+  </si>
+  <si>
+    <t>Improved forecasting data realism by generating additional historical demand data.</t>
+  </si>
+  <si>
+    <t>Enhanced SQL scripts using CTE logic to simulate multi-period demand patterns.</t>
+  </si>
+  <si>
+    <t>Validated ML.NET SSA forecasting output with expanded dataset.</t>
+  </si>
+  <si>
+    <t>Enhanced dashboard UX by displaying selected vendor name and product name directly on the chart section.</t>
+  </si>
+  <si>
+    <t>Removed redundant UI elements such as "Available Model Names" for cleaner interface.</t>
+  </si>
+  <si>
+    <t>Improved layout alignment and readability.</t>
+  </si>
+  <si>
+    <t>Integrated Unsplash API for product image selection in inventory management.</t>
+  </si>
+  <si>
+    <t>Implemented image search and selection within Add Product Lot modal.</t>
+  </si>
+  <si>
+    <t>Stored image metadata (ImageUrl, ImageThumbUrl, PhotographerName) in Product entity and displayed images in UI.</t>
+  </si>
+  <si>
+    <t>Enhanced product selection UX by displaying images alongside product names in dropdowns.</t>
+  </si>
+  <si>
+    <t>Improved user experience by allowing visual identification of products.</t>
+  </si>
+  <si>
+    <t>Added fallback handling for missing images.</t>
+  </si>
+  <si>
+    <t>Improved real-time chat module stability and authentication handling.</t>
+  </si>
+  <si>
+    <t>Resolved SignalR WebSocket connection issues caused by missing JWT token.</t>
+  </si>
+  <si>
+    <t>Updated ChatHub configuration and frontend connection logic to include access token.</t>
+  </si>
+  <si>
+    <t>Enhanced chat UI by replacing user IDs with display names in conversation lists.</t>
+  </si>
+  <si>
+    <t>Implemented backend join queries in ChatController.cs to return vendor and farmer names.</t>
+  </si>
+  <si>
+    <t>Improved conversation selection usability with searchable dropdowns.</t>
+  </si>
+  <si>
+    <t>Optimized API performance by reducing redundant API calls in forecasting and chat modules.</t>
+  </si>
+  <si>
+    <t>Implemented caching and minimized repeated fetch requests in React components.</t>
+  </si>
+  <si>
+    <t>Improved loading times for dashboard and analytics pages.</t>
+  </si>
+  <si>
+    <t>Performed full system integration testing across all modules including forecasting, dispatch, recommendation, chat, and inventory.</t>
+  </si>
+  <si>
+    <t>Verified role-based access control for Farmer and Vendor workflows.</t>
+  </si>
+  <si>
+    <t>Fixed minor bugs related to DTO mismatches and API responses.</t>
+  </si>
+  <si>
+    <t>Conducted final UI/UX refinements across the application.</t>
+  </si>
+  <si>
+    <t>Improved dashboard layout to resemble Power BI style with better spacing and card alignment.</t>
+  </si>
+  <si>
+    <t>Enhanced consistency of buttons, dropdowns, and tables.</t>
+  </si>
+  <si>
+    <t>Final testing and validation of ML.NET SSA forecasting accuracy and system outputs.</t>
+  </si>
+  <si>
+    <t>Verified correctness of forecast results, recommendation outputs, and chart visualizations.</t>
+  </si>
+  <si>
+    <t>Prepared final screenshots, documentation, and report content.</t>
+  </si>
+  <si>
+    <t>Completed final report writing including architecture diagrams, implemented features, evaluation techniques, and AI usage section.</t>
+  </si>
+  <si>
+    <t>Prepared appendix with prompt history and finalized all submission materials.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2160,8 +2992,34 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2183,6 +3041,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2426,7 +3290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2676,35 +3540,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2712,9 +3579,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2726,6 +3590,66 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3027,20 +3951,20 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="87">
+      <c r="A2" s="89">
         <v>46035</v>
       </c>
-      <c r="B2" s="89">
+      <c r="B2" s="91">
         <v>2</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="94" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="92"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="95"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1">
       <c r="A4" s="7"/>
@@ -3107,20 +4031,20 @@
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="87">
+      <c r="A12" s="89">
         <v>46039</v>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="91">
         <v>2</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="94" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="96"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1">
       <c r="A14" s="7"/>
@@ -3203,10 +4127,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="87">
+      <c r="A22" s="89">
         <v>46049</v>
       </c>
-      <c r="B22" s="89">
+      <c r="B22" s="91">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -3214,17 +4138,17 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A23" s="96"/>
-      <c r="B23" s="90"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="87">
+      <c r="A24" s="89">
         <v>46051</v>
       </c>
-      <c r="B24" s="89">
+      <c r="B24" s="91">
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -3232,8 +4156,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A25" s="96"/>
-      <c r="B25" s="90"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="9" t="s">
         <v>22</v>
       </c>
@@ -3250,10 +4174,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="87">
+      <c r="A27" s="89">
         <v>46057</v>
       </c>
-      <c r="B27" s="89">
+      <c r="B27" s="91">
         <v>3</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3261,8 +4185,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="90"/>
+      <c r="A28" s="90"/>
+      <c r="B28" s="92"/>
       <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
@@ -3301,29 +4225,29 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="95"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="88"/>
       <c r="C32" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="95"/>
-      <c r="B33" s="93"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="88"/>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="95"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="95"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="5" t="s">
         <v>32</v>
       </c>
@@ -3521,6 +4445,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A22:A23"/>
@@ -3529,12 +4459,251 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
+  <dimension ref="B2:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="16.5">
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="90">
+      <c r="B3" s="76">
+        <v>46091</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="105">
+      <c r="B4" s="76">
+        <v>46092</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="90">
+      <c r="B5" s="76">
+        <v>46093</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="90">
+      <c r="B6" s="102">
+        <v>46094</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="75">
+      <c r="B7" s="102"/>
+      <c r="C7" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="45" customHeight="1">
+      <c r="B8" s="102">
+        <v>46097</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="120">
+      <c r="B9" s="102"/>
+      <c r="C9" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="102"/>
+      <c r="C10" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
+  <dimension ref="B2:D13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+    <col min="4" max="4" width="54.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="75">
+      <c r="B3" s="100">
+        <v>46099</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="60">
+      <c r="B4" s="100"/>
+      <c r="C4" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="60">
+      <c r="B5" s="100"/>
+      <c r="C5" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="60">
+      <c r="B6" s="100"/>
+      <c r="C6" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="60">
+      <c r="B7" s="100"/>
+      <c r="C7" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="135">
+      <c r="B8" s="99">
+        <v>46100</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="45">
+      <c r="B9" s="99"/>
+      <c r="C9" s="84" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="45">
+      <c r="B10" s="99">
+        <v>46101</v>
+      </c>
+      <c r="C10" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="45">
+      <c r="B11" s="99"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="86" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="30">
+      <c r="B12" s="99"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="30">
+      <c r="B13" s="99"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="86" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4637,6 +5806,1494 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8417A-CD4F-4BA1-A3C5-1FBE85D4FAE2}">
+  <dimension ref="B1:D20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="85.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B2" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="107" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="104" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B3" s="105">
+        <v>46035</v>
+      </c>
+      <c r="C3" s="106">
+        <v>2</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B4" s="105">
+        <v>46035</v>
+      </c>
+      <c r="C4" s="106">
+        <v>1</v>
+      </c>
+      <c r="D4" s="106" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B5" s="105">
+        <v>46036</v>
+      </c>
+      <c r="C5" s="106">
+        <v>4</v>
+      </c>
+      <c r="D5" s="106" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="50.25" thickBot="1">
+      <c r="B6" s="105">
+        <v>46037</v>
+      </c>
+      <c r="C6" s="106">
+        <v>4</v>
+      </c>
+      <c r="D6" s="106" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B7" s="105">
+        <v>46039</v>
+      </c>
+      <c r="C7" s="106">
+        <v>2</v>
+      </c>
+      <c r="D7" s="106" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B8" s="105">
+        <v>46042</v>
+      </c>
+      <c r="C8" s="106">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="106" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B9" s="105">
+        <v>46043</v>
+      </c>
+      <c r="C9" s="106">
+        <v>2</v>
+      </c>
+      <c r="D9" s="106" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B10" s="105">
+        <v>46044</v>
+      </c>
+      <c r="C10" s="106">
+        <v>2</v>
+      </c>
+      <c r="D10" s="106" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B11" s="105">
+        <v>46046</v>
+      </c>
+      <c r="C11" s="106">
+        <v>2</v>
+      </c>
+      <c r="D11" s="106" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B12" s="105">
+        <v>46047</v>
+      </c>
+      <c r="C12" s="106">
+        <v>2</v>
+      </c>
+      <c r="D12" s="106" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B13" s="105">
+        <v>46048</v>
+      </c>
+      <c r="C13" s="106">
+        <v>1</v>
+      </c>
+      <c r="D13" s="106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B14" s="105">
+        <v>46049</v>
+      </c>
+      <c r="C14" s="106">
+        <v>3</v>
+      </c>
+      <c r="D14" s="106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B15" s="105">
+        <v>46051</v>
+      </c>
+      <c r="C15" s="106">
+        <v>4</v>
+      </c>
+      <c r="D15" s="106" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B16" s="105">
+        <v>46055</v>
+      </c>
+      <c r="C16" s="106">
+        <v>2</v>
+      </c>
+      <c r="D16" s="106" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B17" s="105">
+        <v>46057</v>
+      </c>
+      <c r="C17" s="106">
+        <v>3</v>
+      </c>
+      <c r="D17" s="106" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="17.25" thickBot="1">
+      <c r="B18" s="105">
+        <v>46058</v>
+      </c>
+      <c r="C18" s="106">
+        <v>2</v>
+      </c>
+      <c r="D18" s="106" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B19" s="105">
+        <v>46061</v>
+      </c>
+      <c r="C19" s="106">
+        <v>3</v>
+      </c>
+      <c r="D19" s="106" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="33.75" thickBot="1">
+      <c r="B20" s="105">
+        <v>46062</v>
+      </c>
+      <c r="C20" s="106">
+        <v>3</v>
+      </c>
+      <c r="D20" s="106" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC75F75-5F83-48D3-90AF-621E199E850A}">
+  <dimension ref="B3:D162"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="58.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" ht="16.5">
+      <c r="B3" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="108" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="49.5">
+      <c r="B4" s="110">
+        <v>46035</v>
+      </c>
+      <c r="C4" s="113">
+        <v>2</v>
+      </c>
+      <c r="D4" s="111" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="33">
+      <c r="B5" s="110">
+        <v>46035</v>
+      </c>
+      <c r="C5" s="113">
+        <v>1</v>
+      </c>
+      <c r="D5" s="111" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="49.5">
+      <c r="B6" s="110">
+        <v>46036</v>
+      </c>
+      <c r="C6" s="113">
+        <v>4</v>
+      </c>
+      <c r="D6" s="111" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="66">
+      <c r="B7" s="110">
+        <v>46037</v>
+      </c>
+      <c r="C7" s="113">
+        <v>4</v>
+      </c>
+      <c r="D7" s="111" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="33">
+      <c r="B8" s="110">
+        <v>46039</v>
+      </c>
+      <c r="C8" s="113">
+        <v>2</v>
+      </c>
+      <c r="D8" s="111" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="49.5">
+      <c r="B9" s="110">
+        <v>46042</v>
+      </c>
+      <c r="C9" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="111" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="33">
+      <c r="B10" s="110">
+        <v>46043</v>
+      </c>
+      <c r="C10" s="113">
+        <v>2</v>
+      </c>
+      <c r="D10" s="111" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="33">
+      <c r="B11" s="110">
+        <v>46044</v>
+      </c>
+      <c r="C11" s="113">
+        <v>2</v>
+      </c>
+      <c r="D11" s="111" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="33">
+      <c r="B12" s="110">
+        <v>46046</v>
+      </c>
+      <c r="C12" s="113">
+        <v>2</v>
+      </c>
+      <c r="D12" s="111" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="33">
+      <c r="B13" s="110">
+        <v>46047</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2</v>
+      </c>
+      <c r="D13" s="111" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="33">
+      <c r="B14" s="110">
+        <v>46048</v>
+      </c>
+      <c r="C14" s="113">
+        <v>1</v>
+      </c>
+      <c r="D14" s="111" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="49.5">
+      <c r="B15" s="110">
+        <v>46049</v>
+      </c>
+      <c r="C15" s="113">
+        <v>3</v>
+      </c>
+      <c r="D15" s="111" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="33">
+      <c r="B16" s="110">
+        <v>46051</v>
+      </c>
+      <c r="C16" s="113">
+        <v>4</v>
+      </c>
+      <c r="D16" s="111" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="33">
+      <c r="B17" s="110">
+        <v>46055</v>
+      </c>
+      <c r="C17" s="113">
+        <v>2</v>
+      </c>
+      <c r="D17" s="111" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="49.5">
+      <c r="B18" s="110">
+        <v>46057</v>
+      </c>
+      <c r="C18" s="113">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="33">
+      <c r="B19" s="110">
+        <v>46058</v>
+      </c>
+      <c r="C19" s="113">
+        <v>2</v>
+      </c>
+      <c r="D19" s="111" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="49.5">
+      <c r="B20" s="110">
+        <v>46061</v>
+      </c>
+      <c r="C20" s="113">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="49.5">
+      <c r="B21" s="110">
+        <v>46062</v>
+      </c>
+      <c r="C21" s="113">
+        <v>3</v>
+      </c>
+      <c r="D21" s="111" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="17.25" customHeight="1">
+      <c r="B22" s="112">
+        <v>46076</v>
+      </c>
+      <c r="C22" s="115">
+        <v>8</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="30">
+      <c r="B23" s="112"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="112"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="112"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="30">
+      <c r="B26" s="110">
+        <v>46077</v>
+      </c>
+      <c r="C26" s="114" t="s">
+        <v>280</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="30">
+      <c r="B27" s="110">
+        <v>46081</v>
+      </c>
+      <c r="C27" s="114" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="30">
+      <c r="B28" s="110">
+        <v>46082</v>
+      </c>
+      <c r="C28" s="114" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="30">
+      <c r="B29" s="112">
+        <v>46083</v>
+      </c>
+      <c r="C29" s="115" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="30">
+      <c r="B30" s="112"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="30">
+      <c r="B31" s="112"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="60">
+      <c r="B32" s="112"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="45">
+      <c r="B33" s="112"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="45">
+      <c r="B34" s="112"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="45">
+      <c r="B35" s="119">
+        <v>46084</v>
+      </c>
+      <c r="C35" s="115">
+        <v>6</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="45">
+      <c r="B36" s="119"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="45">
+      <c r="B37" s="119"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="45">
+      <c r="B38" s="119">
+        <v>46086</v>
+      </c>
+      <c r="C38" s="115">
+        <v>5</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="45">
+      <c r="B39" s="119"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="30">
+      <c r="B40" s="119"/>
+      <c r="C40" s="115"/>
+      <c r="D40" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="45">
+      <c r="B41" s="119">
+        <v>46088</v>
+      </c>
+      <c r="C41" s="115">
+        <v>6</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="30">
+      <c r="B42" s="119"/>
+      <c r="C42" s="115"/>
+      <c r="D42" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="30">
+      <c r="B43" s="119"/>
+      <c r="C43" s="115"/>
+      <c r="D43" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="30">
+      <c r="B44" s="119"/>
+      <c r="C44" s="115"/>
+      <c r="D44" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="45">
+      <c r="B45" s="119"/>
+      <c r="C45" s="115"/>
+      <c r="D45" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="30">
+      <c r="B46" s="119"/>
+      <c r="C46" s="115"/>
+      <c r="D46" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="45">
+      <c r="B47" s="119">
+        <v>46089</v>
+      </c>
+      <c r="C47" s="115">
+        <v>3</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="30">
+      <c r="B48" s="119"/>
+      <c r="C48" s="115"/>
+      <c r="D48" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="45">
+      <c r="B49" s="119">
+        <v>46090</v>
+      </c>
+      <c r="C49" s="115">
+        <v>7</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="30">
+      <c r="B50" s="119"/>
+      <c r="C50" s="115"/>
+      <c r="D50" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="30">
+      <c r="B51" s="119"/>
+      <c r="C51" s="115"/>
+      <c r="D51" s="15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="45">
+      <c r="B52" s="119"/>
+      <c r="C52" s="115"/>
+      <c r="D52" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="30">
+      <c r="B53" s="119"/>
+      <c r="C53" s="115"/>
+      <c r="D53" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="45">
+      <c r="B54" s="119"/>
+      <c r="C54" s="115"/>
+      <c r="D54" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="60">
+      <c r="B55" s="119"/>
+      <c r="C55" s="115"/>
+      <c r="D55" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="119"/>
+      <c r="C56" s="115"/>
+      <c r="D56" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="15.75">
+      <c r="B57" s="120">
+        <v>46091</v>
+      </c>
+      <c r="C57" s="116">
+        <v>6</v>
+      </c>
+      <c r="D57" s="117" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="31.5">
+      <c r="B58" s="120"/>
+      <c r="C58" s="116"/>
+      <c r="D58" s="117" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" ht="63">
+      <c r="B59" s="120"/>
+      <c r="C59" s="116"/>
+      <c r="D59" s="117" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" ht="78.75">
+      <c r="B60" s="120"/>
+      <c r="C60" s="116"/>
+      <c r="D60" s="117" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" ht="94.5">
+      <c r="B61" s="120"/>
+      <c r="C61" s="116"/>
+      <c r="D61" s="117" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="63">
+      <c r="B62" s="120"/>
+      <c r="C62" s="116"/>
+      <c r="D62" s="117" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" ht="78.75">
+      <c r="B63" s="120"/>
+      <c r="C63" s="116"/>
+      <c r="D63" s="117" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" ht="31.5">
+      <c r="B64" s="121">
+        <v>46092</v>
+      </c>
+      <c r="C64" s="116">
+        <v>6</v>
+      </c>
+      <c r="D64" s="117" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" ht="47.25">
+      <c r="B65" s="121"/>
+      <c r="C65" s="116"/>
+      <c r="D65" s="117" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="63">
+      <c r="B66" s="121"/>
+      <c r="C66" s="116"/>
+      <c r="D66" s="117" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="63">
+      <c r="B67" s="121"/>
+      <c r="C67" s="116"/>
+      <c r="D67" s="117" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="47.25">
+      <c r="B68" s="121">
+        <v>46093</v>
+      </c>
+      <c r="C68" s="116">
+        <v>5</v>
+      </c>
+      <c r="D68" s="117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="47.25">
+      <c r="B69" s="121"/>
+      <c r="C69" s="116"/>
+      <c r="D69" s="117" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="63">
+      <c r="B70" s="121"/>
+      <c r="C70" s="116"/>
+      <c r="D70" s="117" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="47.25">
+      <c r="B71" s="121">
+        <v>46094</v>
+      </c>
+      <c r="C71" s="116">
+        <v>4</v>
+      </c>
+      <c r="D71" s="117" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="47.25">
+      <c r="B72" s="121"/>
+      <c r="C72" s="116"/>
+      <c r="D72" s="117" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" ht="78.75">
+      <c r="B73" s="121"/>
+      <c r="C73" s="116"/>
+      <c r="D73" s="117" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="31.5">
+      <c r="B74" s="121"/>
+      <c r="C74" s="116"/>
+      <c r="D74" s="117" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="63">
+      <c r="B75" s="121">
+        <v>46097</v>
+      </c>
+      <c r="C75" s="116">
+        <v>6</v>
+      </c>
+      <c r="D75" s="117" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" ht="47.25">
+      <c r="B76" s="121"/>
+      <c r="C76" s="116"/>
+      <c r="D76" s="117" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="47.25">
+      <c r="B77" s="121"/>
+      <c r="C77" s="116"/>
+      <c r="D77" s="117" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="47.25">
+      <c r="B78" s="121"/>
+      <c r="C78" s="116"/>
+      <c r="D78" s="117" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" ht="47.25">
+      <c r="B79" s="121"/>
+      <c r="C79" s="116"/>
+      <c r="D79" s="117" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="47.25">
+      <c r="B80" s="121"/>
+      <c r="C80" s="116"/>
+      <c r="D80" s="117" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" ht="47.25">
+      <c r="B81" s="121"/>
+      <c r="C81" s="116"/>
+      <c r="D81" s="117" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" ht="47.25">
+      <c r="B82" s="121"/>
+      <c r="C82" s="116"/>
+      <c r="D82" s="117" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="47.25">
+      <c r="B83" s="121"/>
+      <c r="C83" s="116"/>
+      <c r="D83" s="117" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" ht="31.5">
+      <c r="B84" s="121"/>
+      <c r="C84" s="116"/>
+      <c r="D84" s="117" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" ht="45">
+      <c r="B85" s="119">
+        <v>46099</v>
+      </c>
+      <c r="C85" s="115">
+        <v>4</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" ht="30">
+      <c r="B86" s="119"/>
+      <c r="C86" s="115"/>
+      <c r="D86" s="15" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="45">
+      <c r="B87" s="119"/>
+      <c r="C87" s="115"/>
+      <c r="D87" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" ht="45">
+      <c r="B88" s="119"/>
+      <c r="C88" s="115"/>
+      <c r="D88" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" ht="60">
+      <c r="B89" s="119"/>
+      <c r="C89" s="115"/>
+      <c r="D89" s="15" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" ht="45">
+      <c r="B90" s="119"/>
+      <c r="C90" s="115"/>
+      <c r="D90" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" ht="150">
+      <c r="B91" s="122">
+        <v>46100</v>
+      </c>
+      <c r="C91" s="118">
+        <v>3</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" ht="75">
+      <c r="B92" s="122"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" ht="105">
+      <c r="B93" s="123">
+        <v>46101</v>
+      </c>
+      <c r="C93" s="114">
+        <v>3</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" ht="60">
+      <c r="B94" s="123">
+        <v>46103</v>
+      </c>
+      <c r="C94" s="114">
+        <v>3</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" ht="165">
+      <c r="B95" s="119">
+        <v>46104</v>
+      </c>
+      <c r="C95" s="115">
+        <v>5</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="119"/>
+      <c r="C96" s="115"/>
+      <c r="D96" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" ht="45">
+      <c r="B97" s="17">
+        <v>46105</v>
+      </c>
+      <c r="C97">
+        <v>5</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" ht="30">
+      <c r="D98" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" ht="30">
+      <c r="D99" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="D100" s="15"/>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="17">
+        <v>46106</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" ht="45">
+      <c r="D102" s="15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" ht="30">
+      <c r="D103" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="D104" s="15"/>
+    </row>
+    <row r="105" spans="2:4" ht="30">
+      <c r="B105" s="17">
+        <v>46107</v>
+      </c>
+      <c r="C105">
+        <v>6</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" ht="30">
+      <c r="D106" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" ht="30">
+      <c r="D107" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="D108" s="15"/>
+    </row>
+    <row r="109" spans="2:4" ht="30">
+      <c r="B109" s="17">
+        <v>46108</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" ht="30">
+      <c r="D110" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" ht="30">
+      <c r="D111" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="D112" s="15"/>
+    </row>
+    <row r="113" spans="2:4" ht="30">
+      <c r="B113" s="17">
+        <v>46109</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" ht="30">
+      <c r="D114" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" ht="30">
+      <c r="D115" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="D116" s="15"/>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="17">
+        <v>46110</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" ht="30">
+      <c r="D118" s="15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" ht="30">
+      <c r="D119" s="15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="D120" s="15"/>
+    </row>
+    <row r="121" spans="2:4" ht="30">
+      <c r="B121" s="17">
+        <v>46111</v>
+      </c>
+      <c r="C121">
+        <v>5</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" ht="30">
+      <c r="D122" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" ht="30">
+      <c r="D123" s="15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="D124" s="15"/>
+    </row>
+    <row r="125" spans="2:4" ht="30">
+      <c r="B125" s="17">
+        <v>46112</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" ht="30">
+      <c r="D126" s="15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="D127" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="D128" s="15"/>
+    </row>
+    <row r="129" spans="2:4" ht="30">
+      <c r="B129" s="17">
+        <v>46113</v>
+      </c>
+      <c r="C129">
+        <v>6</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" ht="30">
+      <c r="D130" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" ht="45">
+      <c r="D131" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="D132" s="15"/>
+    </row>
+    <row r="133" spans="2:4" ht="30">
+      <c r="B133" s="17">
+        <v>46114</v>
+      </c>
+      <c r="C133">
+        <v>5</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" ht="30">
+      <c r="D134" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="D135" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="D136" s="15"/>
+    </row>
+    <row r="137" spans="2:4" ht="30">
+      <c r="B137" s="17">
+        <v>46115</v>
+      </c>
+      <c r="C137">
+        <v>6</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" ht="30">
+      <c r="D138" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" ht="30">
+      <c r="D139" s="15" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="D140" s="15"/>
+    </row>
+    <row r="141" spans="2:4" ht="30">
+      <c r="B141" s="17">
+        <v>46116</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" ht="30">
+      <c r="D142" s="15" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" ht="30">
+      <c r="D143" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="D144" s="15"/>
+    </row>
+    <row r="145" spans="2:4" ht="30">
+      <c r="B145" s="17">
+        <v>46117</v>
+      </c>
+      <c r="C145">
+        <v>4</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" ht="30">
+      <c r="D146" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="D147" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="D148" s="15"/>
+    </row>
+    <row r="149" spans="2:4" ht="45">
+      <c r="B149" s="17">
+        <v>46118</v>
+      </c>
+      <c r="C149">
+        <v>5</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" ht="30">
+      <c r="D150" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" ht="30">
+      <c r="D151" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="D152" s="15"/>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="17">
+        <v>46119</v>
+      </c>
+      <c r="C153">
+        <v>4</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" ht="30">
+      <c r="D154" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="D155" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="D156" s="15"/>
+    </row>
+    <row r="157" spans="2:4" ht="30">
+      <c r="B157" s="17">
+        <v>46120</v>
+      </c>
+      <c r="C157">
+        <v>6</v>
+      </c>
+      <c r="D157" s="15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" ht="30">
+      <c r="D158" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" ht="30">
+      <c r="D159" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="D160" s="15"/>
+    </row>
+    <row r="161" spans="2:4" ht="45">
+      <c r="B161" s="17">
+        <v>46121</v>
+      </c>
+      <c r="C161">
+        <v>4</v>
+      </c>
+      <c r="D161" s="15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" ht="30">
+      <c r="D162" s="15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="C49:C56"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="B75:B84"/>
+    <mergeCell ref="C75:C84"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C85:C90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="B57:B63"/>
+    <mergeCell ref="C57:C63"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B35:B37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86F43F-C884-40ED-8D9B-040E7647202D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4645,7 +7302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4CB711-9D7B-4FAA-801C-2959CA58D8D4}">
   <dimension ref="B2:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4667,10 +7324,10 @@
       </c>
     </row>
     <row r="3" spans="2:4">
-      <c r="B3" s="97">
+      <c r="B3" s="98">
         <v>46091</v>
       </c>
-      <c r="C3" s="99">
+      <c r="C3" s="97">
         <v>6</v>
       </c>
       <c r="D3" s="74" t="s">
@@ -4678,52 +7335,52 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30">
-      <c r="B4" s="97"/>
-      <c r="C4" s="99"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="45">
-      <c r="B5" s="97"/>
-      <c r="C5" s="99"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="45">
-      <c r="B6" s="97"/>
-      <c r="C6" s="99"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="75" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="97"/>
-      <c r="C7" s="99"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="45">
-      <c r="B8" s="97"/>
-      <c r="C8" s="99"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="75" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="97"/>
-      <c r="C9" s="99"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="97"/>
       <c r="D9" s="75" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="30">
-      <c r="B10" s="98">
+      <c r="B10" s="99">
         <v>46092</v>
       </c>
-      <c r="C10" s="99">
+      <c r="C10" s="97">
         <v>4</v>
       </c>
       <c r="D10" s="75" t="s">
@@ -4731,31 +7388,31 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="30">
-      <c r="B11" s="98"/>
-      <c r="C11" s="99"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="75" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="43.5">
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="75" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="45">
-      <c r="B13" s="98"/>
-      <c r="C13" s="99"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="97"/>
       <c r="D13" s="75" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
-      <c r="B14" s="98">
+      <c r="B14" s="99">
         <v>46093</v>
       </c>
-      <c r="C14" s="99">
+      <c r="C14" s="97">
         <v>6</v>
       </c>
       <c r="D14" s="75" t="s">
@@ -4763,24 +7420,24 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
-      <c r="B15" s="98"/>
-      <c r="C15" s="99"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="97"/>
       <c r="D15" s="75" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45">
-      <c r="B16" s="98"/>
-      <c r="C16" s="99"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="75" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="30">
-      <c r="B17" s="98">
+      <c r="B17" s="99">
         <v>46094</v>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="97">
         <v>4</v>
       </c>
       <c r="D17" s="75" t="s">
@@ -4788,31 +7445,31 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="30">
-      <c r="B18" s="98"/>
-      <c r="C18" s="99"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="45">
-      <c r="B19" s="98"/>
-      <c r="C19" s="99"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="75" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="30">
-      <c r="B20" s="98"/>
-      <c r="C20" s="99"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="75" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="45">
-      <c r="B21" s="98">
+      <c r="B21" s="99">
         <v>46097</v>
       </c>
-      <c r="C21" s="99">
+      <c r="C21" s="97">
         <v>5</v>
       </c>
       <c r="D21" s="75" t="s">
@@ -4820,87 +7477,87 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="45">
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="97"/>
       <c r="D22" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="30">
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="97"/>
       <c r="D23" s="75" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="30">
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="30">
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="97"/>
       <c r="D25" s="41" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="30">
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="97"/>
       <c r="D26" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="30">
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="97"/>
       <c r="D27" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="30">
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="97"/>
       <c r="D28" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="45">
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="97"/>
       <c r="D29" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="30">
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="97"/>
       <c r="D30" s="75" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B21:B30"/>
     <mergeCell ref="C21:C30"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B21:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F000D01-920E-4EFE-A851-9564F79E29F6}">
   <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5000,7 +7657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31DDE6-DEC7-4DEA-9D6C-A8B6347D6892}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5073,10 +7730,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="135">
-      <c r="B9" s="98">
+      <c r="B9" s="99">
         <v>46100</v>
       </c>
-      <c r="C9" s="99">
+      <c r="C9" s="97">
         <v>3</v>
       </c>
       <c r="D9" s="42" t="s">
@@ -5084,8 +7741,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="75">
-      <c r="B10" s="98"/>
-      <c r="C10" s="99"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="97"/>
       <c r="D10" s="80" t="s">
         <v>252</v>
       </c>
@@ -5141,249 +7798,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8800269A-E4A3-4AFA-9702-5804B7076CB4}">
-  <dimension ref="B2:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="56.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:4" ht="16.5">
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="90">
-      <c r="B3" s="76">
-        <v>46091</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="105">
-      <c r="B4" s="76">
-        <v>46092</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="90">
-      <c r="B5" s="76">
-        <v>46093</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="90">
-      <c r="B6" s="102">
-        <v>46094</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="75">
-      <c r="B7" s="102"/>
-      <c r="C7" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="45" customHeight="1">
-      <c r="B8" s="102">
-        <v>46097</v>
-      </c>
-      <c r="C8" s="78" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="120">
-      <c r="B9" s="102"/>
-      <c r="C9" s="78" t="s">
-        <v>218</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" s="102"/>
-      <c r="C10" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>226</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3B0D-906F-411B-99DF-80BE56DB080E}">
-  <dimension ref="B2:D13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" customWidth="1"/>
-    <col min="4" max="4" width="54.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="67" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="75">
-      <c r="B3" s="100">
-        <v>46099</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="60">
-      <c r="B4" s="100"/>
-      <c r="C4" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="60">
-      <c r="B5" s="100"/>
-      <c r="C5" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="60">
-      <c r="B6" s="100"/>
-      <c r="C6" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="60">
-      <c r="B7" s="100"/>
-      <c r="C7" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="135">
-      <c r="B8" s="98">
-        <v>46100</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="45">
-      <c r="B9" s="98"/>
-      <c r="C9" s="84" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="45">
-      <c r="B10" s="98">
-        <v>46101</v>
-      </c>
-      <c r="C10" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="85" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="45">
-      <c r="B11" s="98"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="86" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="30">
-      <c r="B12" s="98"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="86" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="30">
-      <c r="B13" s="98"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="86" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
 </file>